--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -5,18 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/317e370d51a78cda/Desktop/WEBスクール/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{9AF9EFE5-2776-49DB-982C-4052FEC3339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5246307-BCE6-451A-8A6D-15DD8762A10B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E507B16-0DA6-424C-B521-B10C11C1ECFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
     <sheet name="7-13" sheetId="2" r:id="rId2"/>
     <sheet name="7-14" sheetId="3" r:id="rId3"/>
     <sheet name="7-15" sheetId="4" r:id="rId4"/>
+    <sheet name="7-16" sheetId="5" r:id="rId5"/>
+    <sheet name="7-17" sheetId="6" r:id="rId6"/>
+    <sheet name="7-15 (4)" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="29">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -254,12 +257,94 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>テーブル設計書作成</t>
+    <rPh sb="4" eb="7">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dbの型(tinyintが最小の整数型)</t>
+    <rPh sb="3" eb="4">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイスウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://be-marke.jp/articles/knowhow-website-requirement-definition</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書作成</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テイギショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書のひな型作成</t>
+    <rPh sb="0" eb="5">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ガタサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書で記載すべき具体的な内容はまだ完璧には理解できていない。</t>
+    <rPh sb="0" eb="5">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>グタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンペキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +355,24 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -328,12 +431,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -358,8 +464,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4563,4 +4676,2927 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56A0045-9D53-4CC6-A5D6-D0144024C4B8}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D6DC6F-267C-4F17-A216-7F3B96758D43}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>7</v>
+      </c>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="N35" r:id="rId1" xr:uid="{A8C25DF0-4098-4EB2-BE00-E7B4E276A5FC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5E7C19-79D0-44D8-B74F-21C9B37B6919}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="N37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="N38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E507B16-0DA6-424C-B521-B10C11C1ECFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C0C9CE-5FB9-475B-B23A-65EDAAFE7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="7-15" sheetId="4" r:id="rId4"/>
     <sheet name="7-16" sheetId="5" r:id="rId5"/>
     <sheet name="7-17" sheetId="6" r:id="rId6"/>
-    <sheet name="7-15 (4)" sheetId="7" r:id="rId7"/>
+    <sheet name="7-18" sheetId="7" r:id="rId7"/>
+    <sheet name="7-18 (2)" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="36">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -339,12 +340,64 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>要件定義書作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書記載内容の理解度不足</t>
+    <rPh sb="0" eb="5">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>フソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書作成(指摘取り込み)</t>
+    <rPh sb="8" eb="11">
+      <t>シテキト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://be-marke.jp/articles/knowhow-website-requirement-definition</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://any-inc.jp/blog/20250804/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://genee.jp/contents/requirements-definition-template/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://depart-inc.com/blog/requirement-analysis/</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +428,13 @@
       <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -439,7 +499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -461,15 +521,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1719,53 +1780,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -2685,53 +2746,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -3646,53 +3707,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -4620,53 +4681,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -5590,53 +5651,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -6291,7 +6352,7 @@
       <c r="H35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J35" s="4"/>
@@ -6299,7 +6360,7 @@
       <c r="M35" t="s">
         <v>7</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="N35" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -6317,7 +6378,7 @@
       <c r="H36" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J36" s="4" t="s">
@@ -6327,7 +6388,7 @@
       <c r="M36" t="s">
         <v>7</v>
       </c>
-      <c r="N36" s="9"/>
+      <c r="N36" s="8"/>
     </row>
     <row r="37" spans="4:14" x14ac:dyDescent="0.45">
       <c r="D37" s="2">
@@ -6341,7 +6402,7 @@
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="7"/>
       <c r="J37" s="4"/>
       <c r="L37" s="5"/>
     </row>
@@ -6566,53 +6627,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -6637,6 +6698,1004 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M26" r:id="rId1" xr:uid="{EC34C9C9-994F-448F-A9EF-E427D3BDD11F}"/>
+    <hyperlink ref="M27" r:id="rId2" xr:uid="{7D1DA924-CECD-42A4-812C-7BBF0A4DA130}"/>
+    <hyperlink ref="M28" r:id="rId3" xr:uid="{AD81937B-822F-4E6D-9EC7-3137CA4B61D7}"/>
+    <hyperlink ref="M29" r:id="rId4" xr:uid="{16333196-2270-46A6-B0BF-B10E2FA380C7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A6C636-4572-4F93-A5EA-E88774DAB386}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
     <col min="8" max="8" width="18.09765625" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
@@ -6649,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46218</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -7218,7 +8277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D33" s="2">
         <v>0.85416666666666596</v>
       </c>
@@ -7237,7 +8296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D34" s="2">
         <v>0.874999999999999</v>
       </c>
@@ -7256,7 +8315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D35" s="2">
         <v>0.89583333333333304</v>
       </c>
@@ -7275,7 +8334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D36" s="2">
         <v>0.91666666666666596</v>
       </c>
@@ -7294,7 +8353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D37" s="2">
         <v>0.937499999999999</v>
       </c>
@@ -7315,11 +8374,8 @@
         <v>21</v>
       </c>
       <c r="L37" s="5"/>
-      <c r="N37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="4:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D38" s="2">
         <v>0.95833333333333304</v>
       </c>
@@ -7334,11 +8390,8 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="L38" s="5"/>
-      <c r="N38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="4:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D39" s="2">
         <v>0.97916666666666596</v>
       </c>
@@ -7354,7 +8407,7 @@
       <c r="J39" s="4"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D40" s="2">
         <v>0.999999999999999</v>
       </c>
@@ -7370,7 +8423,7 @@
       <c r="J40" s="4"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D41" s="2">
         <v>1.0208333333333299</v>
       </c>
@@ -7386,7 +8439,7 @@
       <c r="J41" s="4"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D42" s="2">
         <v>1.0416666666666701</v>
       </c>
@@ -7402,7 +8455,7 @@
       <c r="J42" s="4"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D43" s="2">
         <v>1.0625</v>
       </c>
@@ -7418,7 +8471,7 @@
       <c r="J43" s="4"/>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D44" s="2">
         <v>1.0833333333333299</v>
       </c>
@@ -7434,7 +8487,7 @@
       <c r="J44" s="4"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D45" s="2">
         <v>1.1041666666666701</v>
       </c>
@@ -7450,7 +8503,7 @@
       <c r="J45" s="4"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D46" s="2">
         <v>1.125</v>
       </c>
@@ -7466,7 +8519,7 @@
       <c r="J46" s="4"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D47" s="2">
         <v>1.1458333333333299</v>
       </c>
@@ -7482,7 +8535,7 @@
       <c r="J47" s="4"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D48" s="2">
         <v>1.1666666666666701</v>
       </c>
@@ -7543,53 +8596,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C0C9CE-5FB9-475B-B23A-65EDAAFE7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E22CF6-DE59-4233-B8F9-D6F7155CFB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="7-16" sheetId="5" r:id="rId5"/>
     <sheet name="7-17" sheetId="6" r:id="rId6"/>
     <sheet name="7-18" sheetId="7" r:id="rId7"/>
-    <sheet name="7-18 (2)" sheetId="9" r:id="rId8"/>
+    <sheet name="7-19" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="42">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -392,6 +392,63 @@
     <t>https://depart-inc.com/blog/requirement-analysis/</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>https://genee.jp/contents/requirements-definition-template/</t>
+  </si>
+  <si>
+    <t>https://depart-inc.com/blog/requirement-analysis/</t>
+  </si>
+  <si>
+    <t>https://giginc.co.jp/blog/giglab/security-requirement-definition</t>
+  </si>
+  <si>
+    <t>同上</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セキュリティ要件記載項目について</t>
+    <rPh sb="6" eb="8">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能要件の推奨OSの決め方がわからない(一旦最新版を推奨としている)</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>スイショウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イッタン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>サイシンバン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>スイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -527,10 +584,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1780,53 +1837,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -2746,53 +2803,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -3707,53 +3764,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -4681,53 +4738,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -5651,53 +5708,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -6627,53 +6684,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -7175,7 +7232,7 @@
         <v>30</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="10" t="s">
+      <c r="M26" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7198,7 +7255,7 @@
         <v>30</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="10" t="s">
+      <c r="M27" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7217,7 +7274,7 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="10" t="s">
+      <c r="M28" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7236,7 +7293,7 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="10" t="s">
+      <c r="M29" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7622,53 +7679,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -7708,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -8155,9 +8212,18 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" t="s">
+        <v>36</v>
+      </c>
       <c r="L26" s="5"/>
       <c r="M26" t="s">
         <v>7</v>
@@ -8174,9 +8240,18 @@
         <v>0.750000000000001</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" t="s">
+        <v>37</v>
+      </c>
       <c r="L27" s="5"/>
       <c r="M27" t="s">
         <v>7</v>
@@ -8196,6 +8271,9 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
+      <c r="K28" t="s">
+        <v>38</v>
+      </c>
       <c r="L28" s="5"/>
       <c r="M28" t="s">
         <v>7</v>
@@ -8307,9 +8385,16 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" t="s">
         <v>7</v>
@@ -8326,9 +8411,16 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="4"/>
       <c r="L35" s="5"/>
       <c r="M35" t="s">
         <v>7</v>
@@ -8345,9 +8437,16 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="4"/>
       <c r="L36" s="5"/>
       <c r="M36" t="s">
         <v>7</v>
@@ -8364,15 +8463,9 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
@@ -8596,53 +8689,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D470B62-225F-42D0-A3B3-9112C39C8EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AF27C6-86AE-4FEF-8448-C66DD0328357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="8" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="46">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -465,6 +465,23 @@
   </si>
   <si>
     <t>https://ysinc.co.jp/blog/app-requirements-definition/</t>
+  </si>
+  <si>
+    <t>SSLとhttpsの違い</t>
+    <rPh sb="10" eb="11">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サーバー証明書の認証方法</t>
+    <rPh sb="8" eb="10">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -19053,8 +19070,12 @@
       <c r="H34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" t="s">

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AF27C6-86AE-4FEF-8448-C66DD0328357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30AA5B4-6617-4C62-B5DF-B93CCF47E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="8" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="47">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -480,6 +480,16 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部設計作成(テーブル定義)</t>
+    <rPh sb="0" eb="6">
+      <t>ガイブセッケイサクセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2550,13 +2560,19 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.45">
@@ -2570,13 +2586,19 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
       <c r="M35" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.45">

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30AA5B4-6617-4C62-B5DF-B93CCF47E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4887E8-1E8D-4F35-BD01-EBF15C108A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="10" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="47">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -3597,10 +3597,20 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="4"/>
       <c r="L37" s="5"/>
+      <c r="M37" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D38" s="2">

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4887E8-1E8D-4F35-BD01-EBF15C108A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A600F41F-BE11-40C6-A3C5-B5DD963B43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="10" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="12" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="52">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -489,6 +489,44 @@
       <t>ガイブセッケイサクセイ</t>
     </rPh>
     <rPh sb="11" eb="13">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規化のメリットについて</t>
+    <rPh sb="0" eb="3">
+      <t>セイキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規化の手順について</t>
+    <rPh sb="0" eb="3">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://data-viz-lab.com/database-normalization</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/comorevi21/items/9440ff96f74d2db666df</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>設計書作成(テーブル定義)</t>
+    <rPh sb="0" eb="3">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>テイギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4878,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46223</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -5363,12 +5401,19 @@
         <v>0.77083333333333404</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="4"/>
       <c r="L28" s="5"/>
-      <c r="M28" t="s">
-        <v>7</v>
+      <c r="M28" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.45">
@@ -5386,8 +5431,8 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="L29" s="5"/>
-      <c r="M29" t="s">
-        <v>7</v>
+      <c r="M29" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.45">
@@ -5405,9 +5450,6 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="L30" s="5"/>
-      <c r="M30" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D31" s="2">
@@ -5424,9 +5466,6 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="L31" s="5"/>
-      <c r="M31" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D32" s="2">
@@ -5443,11 +5482,8 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="L32" s="5"/>
-      <c r="M32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D33" s="2">
         <v>0.85416666666666596</v>
       </c>
@@ -5462,11 +5498,8 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="L33" s="5"/>
-      <c r="M33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D34" s="2">
         <v>0.874999999999999</v>
       </c>
@@ -5482,11 +5515,8 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
-      <c r="M34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="35" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D35" s="2">
         <v>0.89583333333333304</v>
       </c>
@@ -5497,16 +5527,19 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
-      <c r="M35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D36" s="2">
         <v>0.91666666666666596</v>
       </c>
@@ -5517,16 +5550,19 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
-      <c r="M36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D37" s="2">
         <v>0.937499999999999</v>
       </c>
@@ -5537,12 +5573,19 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="4"/>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="38" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D38" s="2">
         <v>0.95833333333333304</v>
       </c>
@@ -5558,7 +5601,7 @@
       <c r="J38" s="4"/>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="39" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D39" s="2">
         <v>0.97916666666666596</v>
       </c>
@@ -5574,7 +5617,7 @@
       <c r="J39" s="4"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D40" s="2">
         <v>0.999999999999999</v>
       </c>
@@ -5590,7 +5633,7 @@
       <c r="J40" s="4"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D41" s="2">
         <v>1.0208333333333299</v>
       </c>
@@ -5606,7 +5649,7 @@
       <c r="J41" s="4"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D42" s="2">
         <v>1.0416666666666701</v>
       </c>
@@ -5622,7 +5665,7 @@
       <c r="J42" s="4"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D43" s="2">
         <v>1.0625</v>
       </c>
@@ -5638,7 +5681,7 @@
       <c r="J43" s="4"/>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="44" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D44" s="2">
         <v>1.0833333333333299</v>
       </c>
@@ -5654,7 +5697,7 @@
       <c r="J44" s="4"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="45" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D45" s="2">
         <v>1.1041666666666701</v>
       </c>
@@ -5670,7 +5713,7 @@
       <c r="J45" s="4"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="46" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D46" s="2">
         <v>1.125</v>
       </c>
@@ -5686,7 +5729,7 @@
       <c r="J46" s="4"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="47" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D47" s="2">
         <v>1.1458333333333299</v>
       </c>
@@ -5702,7 +5745,7 @@
       <c r="J47" s="4"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D48" s="2">
         <v>1.1666666666666701</v>
       </c>
@@ -5817,6 +5860,10 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M28" r:id="rId1" xr:uid="{E90EEDE9-915A-47FB-B4A1-75A9627754C5}"/>
+    <hyperlink ref="M29" r:id="rId2" xr:uid="{FABC4E20-3C3D-4055-AF2B-86F3A009DE39}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A600F41F-BE11-40C6-A3C5-B5DD963B43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85C09DE-3686-4FE6-848F-5F4812412111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="12" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="59">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -528,6 +528,117 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計書作成(要件定義修正)</t>
+    <rPh sb="0" eb="3">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="12">
+      <t>ヨウケンテイギシュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WBS作成</t>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スケジュールの組み方</t>
+    <rPh sb="7" eb="8">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">要件定義の書き方
+(見やすい要件定義書を書くために
+枠線やフォントを調整)
+</t>
+    <rPh sb="0" eb="4">
+      <t>ヨウケンテイギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ワクセン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4PASxQjmuvw</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.cm-net.co.jp/blog/requirement-definition-sample-word/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今回の課題において要件定義書で記載するべき項目が網羅されているのかどうか
+(ネットの要件定義書の説明では記載項目が多すぎるので
+どの項目が必須かよくわからない)</t>
+    <rPh sb="0" eb="2">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="9" eb="14">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>モウラ</t>
+    </rPh>
+    <rPh sb="42" eb="47">
+      <t>ヨウケンテイギショ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="52" eb="56">
+      <t>キサイコウモク</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ヒッス</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5878,7 +5989,7 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="8" max="8" width="23.69921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
@@ -5890,7 +6001,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46223</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -6204,15 +6315,21 @@
         <v>0.58333333333333404</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L19" s="5"/>
       <c r="M19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="4:13" ht="72" x14ac:dyDescent="0.45">
       <c r="D20" s="2">
         <v>0.58333333333333304</v>
       </c>
@@ -6223,12 +6340,18 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="L20" s="5"/>
-      <c r="M20" t="s">
-        <v>7</v>
+      <c r="M20" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.45">
@@ -6242,12 +6365,18 @@
         <v>0.625</v>
       </c>
       <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L21" s="5"/>
-      <c r="M21" t="s">
-        <v>7</v>
+      <c r="M21" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.45">
@@ -6280,9 +6409,15 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L23" s="5"/>
       <c r="M23" t="s">
         <v>7</v>
@@ -6356,9 +6491,15 @@
         <v>0.750000000000001</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L27" s="5"/>
       <c r="M27" t="s">
         <v>7</v>
@@ -6375,9 +6516,15 @@
         <v>0.77083333333333404</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L28" s="5"/>
       <c r="M28" t="s">
         <v>7</v>
@@ -6470,9 +6617,15 @@
         <v>0.875000000000001</v>
       </c>
       <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L33" s="5"/>
       <c r="M33" t="s">
         <v>7</v>
@@ -6489,9 +6642,15 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" t="s">
@@ -6509,9 +6668,15 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
       <c r="M35" t="s">
@@ -6549,9 +6714,15 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
@@ -6565,9 +6736,15 @@
         <v>0.97916666666666796</v>
       </c>
       <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L38" s="5"/>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.45">
@@ -6829,6 +7006,10 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M20" r:id="rId1" xr:uid="{8E9D0164-D2CA-4BA4-870F-F6CC293F3E75}"/>
+    <hyperlink ref="M21" r:id="rId2" xr:uid="{094B8AF5-3235-4F24-AD01-25039CE446F7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85C09DE-3686-4FE6-848F-5F4812412111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDA1ED3-D62D-423C-9A7E-645C4349EDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="14" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="65">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -642,6 +642,54 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>主キーと外部キー</t>
+    <rPh sb="0" eb="1">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多対多について</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.sejuku.net/blog/54072</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://note.com/yucco72/n/n4383a2dc29b8</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.uncovertruth.co.jp/dx-accelerator/blog/articles/database/067/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>設計書作成(E-R図)</t>
+    <rPh sb="0" eb="3">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -7036,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46223</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -7331,12 +7379,18 @@
         <v>0.5625</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="L18" s="5"/>
-      <c r="M18" t="s">
-        <v>7</v>
+      <c r="M18" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.45">
@@ -7350,12 +7404,18 @@
         <v>0.58333333333333404</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L19" s="5"/>
-      <c r="M19" t="s">
-        <v>7</v>
+      <c r="M19" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.45">
@@ -7373,8 +7433,8 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="L20" s="5"/>
-      <c r="M20" t="s">
-        <v>7</v>
+      <c r="M20" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.45">
@@ -7388,9 +7448,15 @@
         <v>0.625</v>
       </c>
       <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L21" s="5"/>
       <c r="M21" t="s">
         <v>7</v>
@@ -7407,9 +7473,15 @@
         <v>0.64583333333333404</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L22" s="5"/>
       <c r="M22" t="s">
         <v>7</v>
@@ -7464,9 +7536,15 @@
         <v>0.70833333333333404</v>
       </c>
       <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L25" s="5"/>
       <c r="M25" t="s">
         <v>7</v>
@@ -7483,9 +7561,15 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L26" s="5"/>
       <c r="M26" t="s">
         <v>7</v>
@@ -7616,9 +7700,15 @@
         <v>0.875000000000001</v>
       </c>
       <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L33" s="5"/>
       <c r="M33" t="s">
         <v>7</v>
@@ -7635,9 +7725,15 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" t="s">
@@ -7675,9 +7771,15 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
       <c r="M36" t="s">
@@ -7695,9 +7797,15 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
@@ -7975,6 +8083,11 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M18" r:id="rId1" xr:uid="{44BCBC40-6ACF-4179-8033-E80932F958DB}"/>
+    <hyperlink ref="M19" r:id="rId2" xr:uid="{3C613836-CEA8-4EB5-8867-C0618715BE00}"/>
+    <hyperlink ref="M20" r:id="rId3" xr:uid="{ED9E1CE8-4989-483D-BAAC-1B7D394F8BAA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDA1ED3-D62D-423C-9A7E-645C4349EDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC51852B-9E2E-4489-AF06-9E4236EB31B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="14" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="15" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="72">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -690,6 +690,50 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>主キーと一意キーの違い</t>
+    <rPh sb="0" eb="1">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E-R図のカラム省略についてどこまで省略するか。</t>
+    <rPh sb="3" eb="4">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショウリャク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【SQL】プライマリーキーとは？ユニークキーとの違いなどを解説 - DX-Accelerator データ人材常駐支援サービス | UNCOVER TRUTH</t>
+  </si>
+  <si>
+    <t>https://qiita.com/hyougo-suga/items/9ce65df7e2e602d4f24b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/takeda_kaho/articles/9b3e83d7c5c254</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://products.sint.co.jp/blog/primarykey</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>最低限のER図の書き方メモ｜yucco</t>
+  </si>
 </sst>
 </file>
 
@@ -8102,7 +8146,7 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="8" max="8" width="23.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
@@ -8713,13 +8757,19 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
-      <c r="M34" t="s">
-        <v>7</v>
+      <c r="M34" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.45">
@@ -8733,13 +8783,17 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
-      <c r="M35" t="s">
-        <v>7</v>
+      <c r="M35" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.45">
@@ -8758,8 +8812,8 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
-      <c r="M36" t="s">
-        <v>7</v>
+      <c r="M36" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.45">
@@ -8777,6 +8831,9 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="L37" s="5"/>
+      <c r="M37" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D38" s="2">
@@ -8793,6 +8850,9 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="L38" s="5"/>
+      <c r="M38" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D39" s="2">
@@ -9053,6 +9113,13 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M34" r:id="rId1" display="https://www.uncovertruth.co.jp/dx-accelerator/blog/articles/sql/061/" xr:uid="{803CC6D9-B627-4068-95AB-DED2CC2D69A8}"/>
+    <hyperlink ref="M35" r:id="rId2" xr:uid="{81A59764-4537-418B-88A3-34DDE31ADC9F}"/>
+    <hyperlink ref="M36" r:id="rId3" xr:uid="{87F3581D-DFD4-4030-8BC8-1667E3C28416}"/>
+    <hyperlink ref="M37" r:id="rId4" xr:uid="{F2466383-1126-4196-A073-BEC855266788}"/>
+    <hyperlink ref="M38" r:id="rId5" display="https://note.com/yucco72/n/n4383a2dc29b8" xr:uid="{1C99045B-88AC-498A-8261-AEB19C4EE992}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC51852B-9E2E-4489-AF06-9E4236EB31B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468350E5-3355-47FA-8002-EB2F0624C13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="15" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="72">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -8789,7 +8789,9 @@
       <c r="I35" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
       <c r="M35" s="9" t="s">

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468350E5-3355-47FA-8002-EB2F0624C13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A94FEF-A574-49A3-93D7-3FE6FE673C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="15" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="16" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="74">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -734,6 +734,25 @@
   <si>
     <t>最低限のER図の書き方メモ｜yucco</t>
   </si>
+  <si>
+    <t>https://qiita.com/szn-t/items/e05e9e59af3471a724a4</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>テーブル定義書の書き方
+E-R図の書き方
+(WEBアプリを作る際にどんなDBを作ればよいかわかるようにする)</t>
+    <rPh sb="4" eb="7">
+      <t>テイギショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -841,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,6 +891,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9136,7 +9161,7 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="18.09765625" customWidth="1"/>
+    <col min="8" max="8" width="23.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
@@ -9736,7 +9761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="4:13" ht="72" x14ac:dyDescent="0.45">
       <c r="D34" s="2">
         <v>0.874999999999999</v>
       </c>
@@ -9747,13 +9772,19 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="H34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
-      <c r="M34" t="s">
-        <v>7</v>
+      <c r="M34" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.45">
@@ -10087,6 +10118,9 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M34" r:id="rId1" xr:uid="{CF58CFD1-6C0F-4376-A6B2-979FD5B2E2C2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B6860B-4EBD-44C1-81A6-16910100A307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B6A35D-B681-4FC0-BD81-054087EB68A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="17" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="18" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="84">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -779,6 +779,32 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>gitのエラー解決</t>
+    <rPh sb="7" eb="9">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://note.com/koushikagawa/n/nf87b410ee6d6</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/mareinu/items/c3f1b2b7419b7646ac47</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/Hashimoto-Noriaki/items/5d990e21351b331d2aa1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gitのマージ、プル、命名規則について</t>
+    <rPh sb="11" eb="15">
+      <t>メイメイキソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -11145,7 +11171,7 @@
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
     <col min="8" max="8" width="18.09765625" customWidth="1"/>
-    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
     <col min="13" max="13" width="3.8984375" customWidth="1"/>
@@ -11156,7 +11182,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46223</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -11795,13 +11821,19 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
-      <c r="M36" t="s">
-        <v>7</v>
+      <c r="M36" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.45">
@@ -11819,6 +11851,9 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="L37" s="5"/>
+      <c r="M37" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D38" s="2">
@@ -11835,6 +11870,9 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="L38" s="5"/>
+      <c r="M38" s="8" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D39" s="2">
@@ -12095,6 +12133,11 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M36" r:id="rId1" xr:uid="{D5139629-2C4A-4FD3-AEAB-1FB942912043}"/>
+    <hyperlink ref="M37" r:id="rId2" xr:uid="{7B6A0951-2B1F-4E0D-B0DA-859E7A9B4ED1}"/>
+    <hyperlink ref="M38" r:id="rId3" xr:uid="{7AD93400-F438-4308-878B-30C4DA1FF055}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B6A35D-B681-4FC0-BD81-054087EB68A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3435E74-7C5B-4B5A-BC2C-A09211BA25EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="18" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="19" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="記載例" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="7-28" sheetId="18" r:id="rId17"/>
     <sheet name="7-29" sheetId="19" r:id="rId18"/>
     <sheet name="7-30" sheetId="20" r:id="rId19"/>
+    <sheet name="8-1" sheetId="21" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="104">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -805,6 +806,121 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://designup.jp/bootstrap4-cheat-sheet.html</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://hackerthemes.com/bootstrap-cheatsheet/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/ryome/items/27022d194f968b9c3807</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/sun_tomo/items/48bd72be13b141be901b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/taroosg/articles/20240925171800-acaf508d296623</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://shiku-hacker.com/learn-laravel-resource-controller/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://dexall.co.jp/articles/?p=2536</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/etaroid/items/b1024c7d200a75b992fc</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/Sicut_study/items/4f301d000ecee98e78c9</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>リソースコントローラーについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リソースコントローラーの役割</t>
+    <rPh sb="12" eb="14">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各dbごとのコントローラー作成</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bootstrapのコード確認</t>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チートコード等コーディングのための学習準備</t>
+    <rPh sb="6" eb="7">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dokcerの基礎</t>
+    <rPh sb="7" eb="9">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dokcerを使用した動作確認がうまくイメージできていないので
+学習中</t>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ガクシュウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ogis-ri.co.jp/otc/hiroba/technical/docker/part2.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Docker | docker build と Dockerfile でイメージをビルドする基本 #初心者 - Qiita</t>
+  </si>
+  <si>
+    <t>【入門】Docker Desktopとは何ができるの？インストールと使い方 - カゴヤのサーバー研究室</t>
+  </si>
+  <si>
+    <t>https://qiita.com/gahoh/items/7b21377b5c9e3ffddf4a</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -13108,6 +13224,1034 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F709F27A-B438-425D-9CE5-4433D56D41EB}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" ht="36" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="8"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M20" r:id="rId1" xr:uid="{3054EE50-3929-4EDD-BB4A-50734777180C}"/>
+    <hyperlink ref="M21" r:id="rId2" xr:uid="{D92D0BDA-1DE9-421D-9AF9-1F48602C03BB}"/>
+    <hyperlink ref="M22" r:id="rId3" xr:uid="{9DD81A88-4147-472B-8532-F431B82203B8}"/>
+    <hyperlink ref="M23" r:id="rId4" xr:uid="{C262D597-3149-4149-8B69-33CD3C69C5C2}"/>
+    <hyperlink ref="M24" r:id="rId5" xr:uid="{6B6D8536-426F-40A5-ADFD-2F38D42E77E0}"/>
+    <hyperlink ref="M25" r:id="rId6" xr:uid="{B0897FFA-6F2C-4C0A-8FFF-DC981A2795AB}"/>
+    <hyperlink ref="M26" r:id="rId7" xr:uid="{A7C37756-A83B-4B08-996C-D9A0B8149A4A}"/>
+    <hyperlink ref="M27" r:id="rId8" xr:uid="{64A43589-9F2F-426C-8C7A-6073B215F570}"/>
+    <hyperlink ref="M28" r:id="rId9" xr:uid="{F77159EA-89C6-480C-9E22-33B77D00E4BB}"/>
+    <hyperlink ref="M29" r:id="rId10" xr:uid="{3139AD33-9F5B-4EFC-9A7B-313E7DB6AE56}"/>
+    <hyperlink ref="M30" r:id="rId11" display="https://qiita.com/YumaInaura/items/e7155b309e109bc75cf8" xr:uid="{88534FD6-0718-43BA-9F6D-794DE77966EF}"/>
+    <hyperlink ref="M31" r:id="rId12" display="https://www.kagoya.jp/howto/cloud/container/dockerdesktop/" xr:uid="{B6B30112-B259-4691-B616-D0088A271E75}"/>
+    <hyperlink ref="M32" r:id="rId13" xr:uid="{C1151F21-1220-4D16-84F7-5F6F8D66C8EB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC7EE1D-580F-427C-890D-110A283A2526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB25576-5FE1-4D3E-9AE7-2A4C3B9DC6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="21" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="22" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="7-30" sheetId="20" r:id="rId20"/>
     <sheet name="8-1" sheetId="21" r:id="rId21"/>
     <sheet name="8-2" sheetId="22" r:id="rId22"/>
-    <sheet name="8-1 (4)" sheetId="24" r:id="rId23"/>
+    <sheet name="8-3" sheetId="24" r:id="rId23"/>
     <sheet name="8-1 (5)" sheetId="25" r:id="rId24"/>
   </sheets>
   <definedNames>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2346" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="128">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1047,6 +1047,67 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>mysqlとララベルが接続できない原因</t>
+    <rPh sb="11" eb="13">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイグレートエラー原因調査</t>
+    <rPh sb="9" eb="11">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dokcerの基礎、文章の読み方</t>
+    <rPh sb="7" eb="9">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイグレートのエラー原因についてはDokcerのスキル不足が関係していると思うので引き続き学習する。</t>
+    <rPh sb="10" eb="12">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -16477,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -16795,9 +16856,6 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="L19" s="5"/>
-      <c r="M19" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D20" s="2">
@@ -16814,9 +16872,7 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="9" t="s">
-        <v>84</v>
-      </c>
+      <c r="M20" s="9"/>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D21" s="2">
@@ -16833,9 +16889,7 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="9" t="s">
-        <v>85</v>
-      </c>
+      <c r="M21" s="9"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D22" s="2">
@@ -16848,19 +16902,11 @@
         <v>0.64583333333333404</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="M22" s="9"/>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D23" s="2">
@@ -16877,9 +16923,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="9" t="s">
-        <v>87</v>
-      </c>
+      <c r="M23" s="9"/>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D24" s="2">
@@ -16896,9 +16940,7 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="9" t="s">
-        <v>88</v>
-      </c>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D25" s="2">
@@ -16915,9 +16957,7 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="M25" s="9"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D26" s="2">
@@ -16930,19 +16970,11 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="9" t="s">
-        <v>90</v>
-      </c>
+      <c r="M26" s="9"/>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D27" s="2">
@@ -16955,19 +16987,11 @@
         <v>0.750000000000001</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="9" t="s">
-        <v>91</v>
-      </c>
+      <c r="M27" s="9"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D28" s="2">
@@ -16980,19 +17004,11 @@
         <v>0.77083333333333404</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="9" t="s">
-        <v>92</v>
-      </c>
+      <c r="M28" s="9"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D29" s="2">
@@ -17005,19 +17021,11 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="8" t="s">
-        <v>100</v>
-      </c>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D30" s="2">
@@ -17034,11 +17042,9 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="4:13" ht="36" x14ac:dyDescent="0.45">
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D31" s="2">
         <v>0.8125</v>
       </c>
@@ -17049,19 +17055,11 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="G31" s="4"/>
-      <c r="H31" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>99</v>
-      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D32" s="2">
@@ -17074,19 +17072,11 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="G32" s="4"/>
-      <c r="H32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="8" t="s">
-        <v>103</v>
-      </c>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D33" s="2">
@@ -17103,9 +17093,6 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="L33" s="5"/>
-      <c r="M33" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D34" s="2">
@@ -17118,15 +17105,9 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
     </row>
@@ -17141,15 +17122,9 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
     </row>
@@ -17164,9 +17139,15 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
       <c r="M36" s="9"/>
@@ -17182,9 +17163,15 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L37" s="5"/>
       <c r="M37" s="9"/>
     </row>
@@ -17410,7 +17397,9 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
+      <c r="D54" s="12" t="s">
+        <v>127</v>
+      </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
@@ -17464,21 +17453,6 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M20" r:id="rId1" xr:uid="{1B0636E6-522E-4EAB-A46A-F0DE876E3AE1}"/>
-    <hyperlink ref="M21" r:id="rId2" xr:uid="{C4AC5D1D-9C39-4EAF-8356-F371691A4251}"/>
-    <hyperlink ref="M22" r:id="rId3" xr:uid="{A4097969-A3E4-46AE-AD87-63D3D60C804F}"/>
-    <hyperlink ref="M23" r:id="rId4" xr:uid="{4464B69D-A745-4D1B-BCCD-6526BD932F7B}"/>
-    <hyperlink ref="M24" r:id="rId5" xr:uid="{25F817FB-BA1D-4886-9AEF-2FD4C7BCC1FB}"/>
-    <hyperlink ref="M25" r:id="rId6" xr:uid="{BC98A167-56E4-4FE9-9E58-B9F449182479}"/>
-    <hyperlink ref="M26" r:id="rId7" xr:uid="{F669899F-D7DB-4903-B6BC-02AAFA54BD9D}"/>
-    <hyperlink ref="M27" r:id="rId8" xr:uid="{CCE0E2AE-7516-4C4C-B403-CE5F76B27C23}"/>
-    <hyperlink ref="M28" r:id="rId9" xr:uid="{72D227E6-3B56-435F-A377-4C3005356694}"/>
-    <hyperlink ref="M29" r:id="rId10" xr:uid="{3FA22C9F-C7C5-4F75-A426-2762CA4626E9}"/>
-    <hyperlink ref="M30" r:id="rId11" display="https://qiita.com/YumaInaura/items/e7155b309e109bc75cf8" xr:uid="{AD004D2D-8E43-4294-B2D7-5C20614ACAA2}"/>
-    <hyperlink ref="M31" r:id="rId12" display="https://www.kagoya.jp/howto/cloud/container/dockerdesktop/" xr:uid="{343B4B7B-ED09-425C-BB38-4F56B606D258}"/>
-    <hyperlink ref="M32" r:id="rId13" xr:uid="{C289813E-5858-43F6-AAE8-9AAA9B458B7A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB25576-5FE1-4D3E-9AE7-2A4C3B9DC6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D3BF80-D41F-4E28-8F03-12D9486A2848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="22" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="130">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1108,6 +1108,14 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YfaB3PJv1f0</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/n_yamadamadamada/items/5021aa265bd246a0eb90</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -16856,6 +16864,9 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D20" s="2">
@@ -16872,7 +16883,9 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="9"/>
+      <c r="M20" s="9" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D21" s="2">
@@ -16889,7 +16902,9 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="9"/>
+      <c r="M21" s="9" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D22" s="2">
@@ -16906,7 +16921,9 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="9"/>
+      <c r="M22" s="9" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D23" s="2">
@@ -17453,6 +17470,12 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M19" r:id="rId1" xr:uid="{B82A8FFD-1AA0-4590-BBEE-2D6F94A4306F}"/>
+    <hyperlink ref="M20" r:id="rId2" xr:uid="{F3380D5A-B1D3-485A-9849-B1000370A028}"/>
+    <hyperlink ref="M21" r:id="rId3" xr:uid="{B55D1BC5-C64D-4FCF-BD25-E79E01418B24}"/>
+    <hyperlink ref="M22" r:id="rId4" xr:uid="{60D028C7-6360-42C0-9B2B-6E58292D9B22}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D3BF80-D41F-4E28-8F03-12D9486A2848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC28948-0B38-4CEC-8058-B5CEA66FF466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="22" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="23" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <sheet name="8-1" sheetId="21" r:id="rId21"/>
     <sheet name="8-2" sheetId="22" r:id="rId22"/>
     <sheet name="8-3" sheetId="24" r:id="rId23"/>
-    <sheet name="8-1 (5)" sheetId="25" r:id="rId24"/>
+    <sheet name="8-4" sheetId="25" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="142">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1116,6 +1116,73 @@
     <t>https://qiita.com/n_yamadamadamada/items/5021aa265bd246a0eb90</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=B5tSZr_QqXw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/GWYx-7OwNqg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/UMyub8d7q4s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/5qrIZlyk53w</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/g_C1CVvL5Dc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/XH1b9Tbz7yY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3yZtYs27pnA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lCMFOEpgRaU </t>
+  </si>
+  <si>
+    <t>dokcerの基礎用語(イメージ、composeなど)の意味</t>
+    <rPh sb="7" eb="9">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウゴ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dokcerの基礎、マイグレートエラー原因調査</t>
+    <rPh sb="7" eb="9">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイグレートエラー原因</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引き続きdokcerの学習を実施しているがまだエラー解決できていない。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -17490,8 +17557,8 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
     <col min="13" max="13" width="3.8984375" customWidth="1"/>
@@ -17502,7 +17569,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46233</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -17839,8 +17906,8 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="9" t="s">
-        <v>84</v>
+      <c r="M20" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.45">
@@ -17858,8 +17925,8 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="9" t="s">
-        <v>85</v>
+      <c r="M21" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.45">
@@ -17873,18 +17940,12 @@
         <v>0.64583333333333404</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="9" t="s">
-        <v>86</v>
+      <c r="M22" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.45">
@@ -17902,8 +17963,8 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="9" t="s">
-        <v>87</v>
+      <c r="M23" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.45">
@@ -17921,8 +17982,8 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="9" t="s">
-        <v>88</v>
+      <c r="M24" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.45">
@@ -17940,8 +18001,8 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="9" t="s">
-        <v>89</v>
+      <c r="M25" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.45">
@@ -17955,18 +18016,12 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="9" t="s">
-        <v>90</v>
+      <c r="M26" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.45">
@@ -17980,18 +18035,12 @@
         <v>0.750000000000001</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="9" t="s">
-        <v>91</v>
+      <c r="M27" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.45">
@@ -18005,19 +18054,11 @@
         <v>0.77083333333333404</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="9" t="s">
-        <v>92</v>
-      </c>
+      <c r="M28" s="9"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D29" s="2">
@@ -18030,19 +18071,11 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="8" t="s">
-        <v>100</v>
-      </c>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D30" s="2">
@@ -18059,11 +18092,9 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="4:13" ht="36" x14ac:dyDescent="0.45">
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D31" s="2">
         <v>0.8125</v>
       </c>
@@ -18074,19 +18105,11 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="G31" s="4"/>
-      <c r="H31" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>99</v>
-      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D32" s="2">
@@ -18099,19 +18122,11 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="G32" s="4"/>
-      <c r="H32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="8" t="s">
-        <v>103</v>
-      </c>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D33" s="2">
@@ -18128,9 +18143,6 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="L33" s="5"/>
-      <c r="M33" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D34" s="2">
@@ -18143,15 +18155,9 @@
         <v>0.89583333333333404</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
     </row>
@@ -18167,13 +18173,13 @@
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
@@ -18189,8 +18195,12 @@
         <v>0.937500000000001</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
@@ -18435,7 +18445,9 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
+      <c r="D54" s="12" t="s">
+        <v>141</v>
+      </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
@@ -18489,21 +18501,6 @@
     <mergeCell ref="D54:J58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M20" r:id="rId1" xr:uid="{20F78B14-CAFD-49F6-8204-19E94DFD3EC3}"/>
-    <hyperlink ref="M21" r:id="rId2" xr:uid="{BF05FE0F-9791-492B-98DE-B8974AA7BC76}"/>
-    <hyperlink ref="M22" r:id="rId3" xr:uid="{9D683DFB-412C-42F8-AD48-A8B890F47A9D}"/>
-    <hyperlink ref="M23" r:id="rId4" xr:uid="{46EFB361-FB0C-44BC-AF7B-31EFF0951B4E}"/>
-    <hyperlink ref="M24" r:id="rId5" xr:uid="{59E87FD4-59B0-42D7-BD36-4D3372053A3A}"/>
-    <hyperlink ref="M25" r:id="rId6" xr:uid="{F81A69A4-FBF1-4E68-9D4C-85433C4FEDFA}"/>
-    <hyperlink ref="M26" r:id="rId7" xr:uid="{4B89C589-0662-41D3-A58C-286CCE8C2C8B}"/>
-    <hyperlink ref="M27" r:id="rId8" xr:uid="{429825EC-71A5-4C7C-A4B3-38E4732E7084}"/>
-    <hyperlink ref="M28" r:id="rId9" xr:uid="{DEE8B471-3318-49C8-84D1-51D14A26D458}"/>
-    <hyperlink ref="M29" r:id="rId10" xr:uid="{3B56E7DC-3723-48ED-9C55-A78F19D57A1D}"/>
-    <hyperlink ref="M30" r:id="rId11" display="https://qiita.com/YumaInaura/items/e7155b309e109bc75cf8" xr:uid="{9867BF59-2A81-4492-8399-912C275F781B}"/>
-    <hyperlink ref="M31" r:id="rId12" display="https://www.kagoya.jp/howto/cloud/container/dockerdesktop/" xr:uid="{2239C290-EEE2-4025-9C58-51458BD8AA64}"/>
-    <hyperlink ref="M32" r:id="rId13" xr:uid="{C8064885-9708-4082-865E-CD2E979C2325}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC28948-0B38-4CEC-8058-B5CEA66FF466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F594276-D00E-400E-8F53-4CB0A4087531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="23" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="24" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="8-2" sheetId="22" r:id="rId22"/>
     <sheet name="8-3" sheetId="24" r:id="rId23"/>
     <sheet name="8-4" sheetId="25" r:id="rId24"/>
+    <sheet name="8-5" sheetId="26" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="145">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1183,6 +1184,56 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>【Docker入門】Docker Composeを使ったphpMyAdminとMySQLコンテナの作成 - YouTube</t>
+  </si>
+  <si>
+    <t>引き続きdokcerの学習を実施しているがまだエラー解決できていない。
+環境変数あたりの設定が足りていない気がするので明日はそちらを深く調べる予定。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>カンキョウヘンスウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>アス</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>シラ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Docker ComposeでMySQLコンテナを立てる。そもそもDBサーバってなに？ #Docker - Qiita</t>
+  </si>
 </sst>
 </file>
 
@@ -1290,7 +1341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,6 +1378,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18505,6 +18559,956 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0076AB3-51EE-48BC-AEC0-7BB9E3567B7B}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="8"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="8"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M38" r:id="rId1" display="https://www.youtube.com/watch?v=NE-KJHS50cc" xr:uid="{A3252E2C-09FF-4FD8-B399-4CD7B6889EEE}"/>
+    <hyperlink ref="M39" r:id="rId2" display="https://qiita.com/n_yamadamadamada/items/5021aa265bd246a0eb90" xr:uid="{A37D1DBC-BF82-46DD-8C1D-EDC627281A6D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F594276-D00E-400E-8F53-4CB0A4087531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB7938F-A349-49F0-B6D5-7116FC051E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="24" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="25" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="8-3" sheetId="24" r:id="rId23"/>
     <sheet name="8-4" sheetId="25" r:id="rId24"/>
     <sheet name="8-5" sheetId="26" r:id="rId25"/>
+    <sheet name="8-6" sheetId="27" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="155">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1234,6 +1235,89 @@
   <si>
     <t>Docker ComposeでMySQLコンテナを立てる。そもそもDBサーバってなに？ #Docker - Qiita</t>
   </si>
+  <si>
+    <t>マイグレートエラー原因解決(lalavelコマンドはコンテナに入って打つことで解決)</t>
+    <rPh sb="11" eb="13">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NE-KJHS50cc</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/mineaki27th/items/2fec99060f1c97ec2892</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/wanwanwan/items/66e0fc9d2730647c9f42</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/tsukiji0718/items/602871a146ed79909d56</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YfaB3PJv1f0</t>
+  </si>
+  <si>
+    <t>エラーについては解決した。
+コンテナの中に入ってコマンドを打つことで解決した。
+(envファイルの設定に変更なし)</t>
+    <rPh sb="8" eb="10">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同上、Bootstrapのひな型探し</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://getbootstrap.jp/docs/4.3/examples/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/shotets/items/50afa5a215c54abadb00</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -1377,10 +1461,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2670,53 +2754,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -3671,53 +3755,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -4648,53 +4732,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -5623,53 +5707,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -6588,53 +6672,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -7558,53 +7642,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -8593,53 +8677,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -9622,53 +9706,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -10610,53 +10694,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -11588,53 +11672,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -12569,53 +12653,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -13548,53 +13632,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -14525,53 +14609,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -15543,53 +15627,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -16569,53 +16653,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -17535,55 +17619,55 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -18499,55 +18583,55 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -19445,55 +19529,55 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -19504,6 +19588,973 @@
   <hyperlinks>
     <hyperlink ref="M38" r:id="rId1" display="https://www.youtube.com/watch?v=NE-KJHS50cc" xr:uid="{A3252E2C-09FF-4FD8-B399-4CD7B6889EEE}"/>
     <hyperlink ref="M39" r:id="rId2" display="https://qiita.com/n_yamadamadamada/items/5021aa265bd246a0eb90" xr:uid="{A37D1DBC-BF82-46DD-8C1D-EDC627281A6D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B0924B-EDEF-4DF7-8455-9FD768646ACB}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="8"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="8"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+      <c r="M41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M36" r:id="rId1" xr:uid="{CBCA01E6-7C42-40FE-8ECA-1C8326F5CA9D}"/>
+    <hyperlink ref="M37" r:id="rId2" xr:uid="{742D03DA-E072-4182-BFCD-011533834028}"/>
+    <hyperlink ref="M38" r:id="rId3" xr:uid="{CF8662B5-46A8-4F9B-A01F-06211F024E70}"/>
+    <hyperlink ref="M39" r:id="rId4" xr:uid="{8EBB6F99-E793-45DC-93CA-722723718C34}"/>
+    <hyperlink ref="M40" r:id="rId5" xr:uid="{1361081E-7D7A-4A43-9DA1-AF07DAC5EB7A}"/>
+    <hyperlink ref="M42" r:id="rId6" xr:uid="{FB471E70-2397-402C-B9F7-4B0819A60C98}"/>
+    <hyperlink ref="M43" r:id="rId7" xr:uid="{01F5FF4A-CDD2-4C2C-9352-C8DC3581CAE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20417,53 +21468,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -21378,53 +22429,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -22352,53 +23403,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -23322,53 +24373,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -24298,53 +25349,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -25293,53 +26344,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>
@@ -26303,53 +27354,53 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
       <c r="L56" s="5"/>
     </row>
     <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
       <c r="L57" s="5"/>
     </row>
     <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
       <c r="L58" s="5"/>
     </row>
   </sheetData>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB7938F-A349-49F0-B6D5-7116FC051E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A9464-711D-41E8-B9B6-CD344DC77C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="25" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="15" activeTab="26" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="8-4" sheetId="25" r:id="rId24"/>
     <sheet name="8-5" sheetId="26" r:id="rId25"/>
     <sheet name="8-6" sheetId="27" r:id="rId26"/>
+    <sheet name="8-7" sheetId="28" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="162">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1318,6 +1319,58 @@
     <t>https://qiita.com/shotets/items/50afa5a215c54abadb00</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>Bootstrapのひな型探し、TOP画面作成</t>
+    <rPh sb="12" eb="13">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ガメンサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ACGuu7t_7-E</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://laraweb.net/surrounding/5962/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/mumucochimu/items/cde51b0ed6bde5a16627</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://startbootstrap.com/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bootstrapのメリット(作業効率UP,レスポンシブ等)</t>
+    <rPh sb="15" eb="19">
+      <t>サギョウコウリツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bootstrapを学習しながらTOP画面を作成中</t>
+    <rPh sb="10" eb="12">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -20560,6 +20613,961 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A3349F-C52E-4B58-A37E-71036D68DB5F}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="8"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="8"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M36" r:id="rId1" xr:uid="{BBF9406C-3D81-45B3-91C2-7FB238CBE45A}"/>
+    <hyperlink ref="M37" r:id="rId2" xr:uid="{093CB00E-4167-40AB-A7A9-AF7023DF76C8}"/>
+    <hyperlink ref="M38" r:id="rId3" xr:uid="{C2094E03-DAE8-4D01-B0D0-B0E46DA2E47F}"/>
+    <hyperlink ref="M39" r:id="rId4" xr:uid="{09E56B01-8019-4952-A332-D323951429D1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A9464-711D-41E8-B9B6-CD344DC77C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A21B38-4B28-4128-8449-559BA16B741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="15" activeTab="26" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="16" activeTab="28" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -40,6 +40,8 @@
     <sheet name="8-5" sheetId="26" r:id="rId25"/>
     <sheet name="8-6" sheetId="27" r:id="rId26"/>
     <sheet name="8-7" sheetId="28" r:id="rId27"/>
+    <sheet name="8-8" sheetId="30" r:id="rId28"/>
+    <sheet name="8-9" sheetId="29" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="170">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1371,6 +1373,71 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Bootstrap学習、TOP画面作成</t>
+    <rPh sb="9" eb="11">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ガメンサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTNLタグ(iタグ(html))、Bootstrap(containerクラス、Bootstrapクラス(rowクラス、colクラス)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.tohoho-web.com/bootstrap/forms.html</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://laraweb.net/surrounding/6217/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://skillhub.jp/courses/549/lessons/4234</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>同上＋htmlスキル登録画面作成</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同上＋htmlコントローラーファイル作成中</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bootstrapを学習しながらTOP画面、htmlスキル登録画面、htmlコントローラーファイルを作成中</t>
+    <rPh sb="10" eb="12">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -21568,6 +21635,1973 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295EA6C7-41C0-4647-800C-73142E5C7312}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="8"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="8"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M36" r:id="rId1" xr:uid="{8AD0276C-0BC7-4573-BBBF-B9DD4D22E126}"/>
+    <hyperlink ref="M37" r:id="rId2" xr:uid="{77A379F0-9F38-4EA5-BFC1-A09581F56E7D}"/>
+    <hyperlink ref="M38" r:id="rId3" xr:uid="{C7A0EA88-C893-49B2-948C-9F6A278ECC23}"/>
+    <hyperlink ref="M39" r:id="rId4" xr:uid="{F8AFE70E-7A77-4764-9D6E-8B82902EC45C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDD0B73-E798-4DEF-9280-3A586EB1328D}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M25" r:id="rId1" xr:uid="{5E1C5B1D-636F-4C6B-88E9-7347E2C4E9E1}"/>
+    <hyperlink ref="M26" r:id="rId2" xr:uid="{16F2E586-BD17-46EB-B4F5-8FF3A6CE6293}"/>
+    <hyperlink ref="M27" r:id="rId3" xr:uid="{27DDE024-BD1C-4970-88A4-2E8500D85DE7}"/>
+    <hyperlink ref="M28" r:id="rId4" xr:uid="{260A0FAA-DDC8-4F47-9A8D-ACC4A402D604}"/>
+    <hyperlink ref="M29" r:id="rId5" xr:uid="{CD25B44B-64BF-49FF-A174-A024B10F0D99}"/>
+    <hyperlink ref="M30" r:id="rId6" xr:uid="{C40C0A64-E51B-4AB5-9B99-6EBD64239DE5}"/>
+    <hyperlink ref="M31" r:id="rId7" xr:uid="{A86C52DB-3B84-4310-BEAD-D5A5620A3797}"/>
+    <hyperlink ref="M32" r:id="rId8" xr:uid="{47B9A2B4-E07F-4F1D-BAB6-71F36EC69364}"/>
+    <hyperlink ref="M33" r:id="rId9" xr:uid="{37ADA704-193C-4699-9BE7-AA97AB2943D1}"/>
+    <hyperlink ref="M34" r:id="rId10" xr:uid="{5A1D0231-E933-4C44-B389-BD6CA98BC280}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A21B38-4B28-4128-8449-559BA16B741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D729B-3E1A-4610-B09B-8CC831213C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="16" activeTab="28" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="178">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1388,53 +1388,125 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.tohoho-web.com/bootstrap/forms.html</t>
+    <t>Bootstrap学習、TOP画面作成中、
+htmlスキル登録画面作成中、
+htmlコントローラーファイル作成中</t>
+    <rPh sb="9" eb="11">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ガメンサクセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://creatorquest.jp/lessons/html/absolutepath-relativepath/</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>https://laraweb.net/surrounding/6217/</t>
+    <t>https://qiita.com/Hashimoto-Noriaki/items/8fa2a72b7b5f3c295329</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>https://skillhub.jp/courses/549/lessons/4234</t>
+    <t>https://frontendlab.magicgifted.com/laravelroutingtaisyo/</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>同上＋htmlスキル登録画面作成</t>
+    <t>https://qiita.com/kuroudoart/items/44eca2150f102ba7fdb4</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://terakoya.sejuku.net/question/detail/51748</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/Hashimoto-Noriaki/items/77a1fcf2820d90d8ed21</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://terakoya.sejuku.net/question/detail/48746</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1s-_XKtOZ-I</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://kobesoft.co.jp/tech/learn/laravel-basics/02/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://biz.addisteria.com/laravel_carbon/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>同上、各テーブルのモデル作成</t>
     <rPh sb="0" eb="2">
       <t>ドウジョウ</t>
     </rPh>
-    <rPh sb="10" eb="14">
-      <t>トウロクガメン</t>
+    <rPh sb="3" eb="4">
+      <t>カク</t>
     </rPh>
-    <rPh sb="14" eb="16">
+    <rPh sb="12" eb="14">
       <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>同上＋htmlコントローラーファイル作成中</t>
-    <rPh sb="0" eb="2">
-      <t>ドウジョウ</t>
+    <t>リモートコントローラーの書き方(::CLASSは不要など)</t>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
     </rPh>
-    <rPh sb="18" eb="20">
-      <t>サクセイ</t>
+    <rPh sb="14" eb="15">
+      <t>カタ</t>
     </rPh>
-    <rPh sb="20" eb="21">
-      <t>チュウ</t>
+    <rPh sb="24" eb="26">
+      <t>フヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Bootstrapを学習しながらTOP画面、htmlスキル登録画面、htmlコントローラーファイルを作成中</t>
-    <rPh sb="10" eb="12">
-      <t>ガクシュウ</t>
+    <t>引き続きTOP画面、htmlスキル登録画面、htmlコントローラーファイルを作成中
+登録画面から値を登録できることは確認ずみ。
+ビューの指摘は取り込めていない。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
     </rPh>
-    <rPh sb="19" eb="21">
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="50" eb="53">
+    <rPh sb="38" eb="41">
       <t>サクセイチュウ</t>
+    </rPh>
+    <rPh sb="42" eb="46">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>コ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -22604,7 +22676,7 @@
     <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.5" customWidth="1"/>
@@ -22616,7 +22688,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -23030,19 +23102,11 @@
         <v>0.70833333333333404</v>
       </c>
       <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="9" t="s">
-        <v>157</v>
-      </c>
+      <c r="M25" s="9"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D26" s="2">
@@ -23055,21 +23119,13 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" ht="54" x14ac:dyDescent="0.45">
       <c r="D27" s="2">
         <v>0.72916666666666596</v>
       </c>
@@ -23080,18 +23136,18 @@
         <v>0.750000000000001</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="4" t="s">
-        <v>39</v>
+      <c r="H27" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="9" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.45">
@@ -23105,12 +23161,16 @@
         <v>0.77083333333333404</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="J28" s="4"/>
       <c r="L28" s="5"/>
       <c r="M28" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.45">
@@ -23129,7 +23189,7 @@
       <c r="J29" s="4"/>
       <c r="L29" s="5"/>
       <c r="M29" s="9" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.45">
@@ -23148,7 +23208,7 @@
       <c r="J30" s="4"/>
       <c r="L30" s="5"/>
       <c r="M30" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.45">
@@ -23167,7 +23227,7 @@
       <c r="J31" s="6"/>
       <c r="L31" s="5"/>
       <c r="M31" s="9" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.45">
@@ -23186,7 +23246,7 @@
       <c r="J32" s="4"/>
       <c r="L32" s="5"/>
       <c r="M32" s="9" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.45">
@@ -23201,17 +23261,15 @@
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J33" s="4"/>
       <c r="L33" s="5"/>
       <c r="M33" s="9" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.45">
@@ -23226,18 +23284,16 @@
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="5"/>
       <c r="M34" s="9" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.45">
@@ -23251,11 +23307,18 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="5"/>
+      <c r="M35" s="9" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D36" s="2">
@@ -23273,7 +23336,9 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="9"/>
+      <c r="M36" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D37" s="2">
@@ -23287,16 +23352,16 @@
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J37" s="4"/>
       <c r="L37" s="5"/>
-      <c r="M37" s="9"/>
+      <c r="M37" s="9" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.45">
       <c r="D38" s="2">
@@ -23309,15 +23374,9 @@
         <v>0.97916666666666796</v>
       </c>
       <c r="G38" s="4"/>
-      <c r="H38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
       <c r="L38" s="5"/>
       <c r="M38" s="9"/>
     </row>
@@ -23531,7 +23590,7 @@
     </row>
     <row r="54" spans="4:12" x14ac:dyDescent="0.45">
       <c r="D54" s="12" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
@@ -23587,16 +23646,17 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="M25" r:id="rId1" xr:uid="{5E1C5B1D-636F-4C6B-88E9-7347E2C4E9E1}"/>
-    <hyperlink ref="M26" r:id="rId2" xr:uid="{16F2E586-BD17-46EB-B4F5-8FF3A6CE6293}"/>
-    <hyperlink ref="M27" r:id="rId3" xr:uid="{27DDE024-BD1C-4970-88A4-2E8500D85DE7}"/>
-    <hyperlink ref="M28" r:id="rId4" xr:uid="{260A0FAA-DDC8-4F47-9A8D-ACC4A402D604}"/>
-    <hyperlink ref="M29" r:id="rId5" xr:uid="{CD25B44B-64BF-49FF-A174-A024B10F0D99}"/>
-    <hyperlink ref="M30" r:id="rId6" xr:uid="{C40C0A64-E51B-4AB5-9B99-6EBD64239DE5}"/>
-    <hyperlink ref="M31" r:id="rId7" xr:uid="{A86C52DB-3B84-4310-BEAD-D5A5620A3797}"/>
-    <hyperlink ref="M32" r:id="rId8" xr:uid="{47B9A2B4-E07F-4F1D-BAB6-71F36EC69364}"/>
-    <hyperlink ref="M33" r:id="rId9" xr:uid="{37ADA704-193C-4699-9BE7-AA97AB2943D1}"/>
-    <hyperlink ref="M34" r:id="rId10" xr:uid="{5A1D0231-E933-4C44-B389-BD6CA98BC280}"/>
+    <hyperlink ref="M27" r:id="rId1" xr:uid="{42742203-1F0B-4B7B-8250-188B0BAB7794}"/>
+    <hyperlink ref="M28" r:id="rId2" xr:uid="{D953A774-3735-4CD1-980D-71294588F77D}"/>
+    <hyperlink ref="M29" r:id="rId3" xr:uid="{BA5B4845-49F1-40C1-B5C9-C1FBE82042B1}"/>
+    <hyperlink ref="M30" r:id="rId4" xr:uid="{B1605E80-2EB3-4507-A9A1-545F033E583D}"/>
+    <hyperlink ref="M31" r:id="rId5" xr:uid="{DE07454A-3B06-41F5-9AF4-D7FDB291EC2F}"/>
+    <hyperlink ref="M32" r:id="rId6" xr:uid="{A1537962-5504-4F22-B9FA-E2D3874DAF75}"/>
+    <hyperlink ref="M33" r:id="rId7" xr:uid="{7D2C276B-8388-4429-8BA7-5F09A1BB66A5}"/>
+    <hyperlink ref="M34" r:id="rId8" xr:uid="{B3EB384A-22D8-4F5D-ADD7-34B3F0D2FFF9}"/>
+    <hyperlink ref="M35" r:id="rId9" xr:uid="{6991AD1F-B6E9-4D3A-B91A-FCD9FAAD7D14}"/>
+    <hyperlink ref="M36" r:id="rId10" xr:uid="{7ADF4416-2797-4451-B804-F3EE76018C5A}"/>
+    <hyperlink ref="M37" r:id="rId11" xr:uid="{BBAABAF7-2506-4904-AF45-FEBE43A3B77E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D729B-3E1A-4610-B09B-8CC831213C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F491C-A918-43CE-AD5F-7B577E3ADFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="16" activeTab="28" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="29" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -42,6 +42,7 @@
     <sheet name="8-7" sheetId="28" r:id="rId27"/>
     <sheet name="8-8" sheetId="30" r:id="rId28"/>
     <sheet name="8-9" sheetId="29" r:id="rId29"/>
+    <sheet name="8-10" sheetId="31" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="183">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1510,6 +1511,70 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>メタタグ(meta tag)とは？書き方と例文を覚えよう - ミエルカマーケティングジャーナル</t>
+  </si>
+  <si>
+    <t>HTML入門2022header,main,aside,footerレイアウトに使うタグの使い方、書き方9分カンタン解説</t>
+  </si>
+  <si>
+    <t>資料読み込み(メタタグ、ヘッダータグなどタグの復習)</t>
+    <rPh sb="0" eb="3">
+      <t>シリョウヨ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグの意味を再度確認</t>
+    <rPh sb="3" eb="5">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>サイドカクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本日は資料読み込みのみ、コードの進捗はなし。
+タグの意味については忘れていることも多いと感じたので復習した。</t>
+    <rPh sb="0" eb="2">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>フクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -24628,6 +24693,957 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA70BF8E-E61E-4DD4-B092-05B5B84C146C}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M36" r:id="rId1" display="https://mieru-ca.com/blog/meta-tag/" xr:uid="{38B00C5B-1901-45FC-9897-861B754CD3C3}"/>
+    <hyperlink ref="M37" r:id="rId2" display="https://www.youtube.com/watch?v=PT7jS6LMkSE" xr:uid="{F965D079-3405-42C2-A5C8-C47AD31A5088}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F491C-A918-43CE-AD5F-7B577E3ADFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A138BB4-7EF5-4466-A2D0-CDE54D22AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="29" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="30" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet name="8-8" sheetId="30" r:id="rId28"/>
     <sheet name="8-9" sheetId="29" r:id="rId29"/>
     <sheet name="8-10" sheetId="31" r:id="rId30"/>
+    <sheet name="8-11" sheetId="32" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="196">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1575,6 +1576,91 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://qiita.com/miriwo/items/7a5f066a42f32467e894</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/oyahiroki/items/bfafb33d09383fb91844</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://teratail.com/questions/250471</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/nakanishi03/items/c80a16b9b9796c25f890</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://favicon.c-cloud.co.jp/blog/laravel-favicon-setup</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://iconscout.com/jp</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://favicon.c-cloud.co.jp/generator</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.weblab.co.jp/blog/staff/seo/1182.html</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://job-info.hateblo.jp/entry/2024/08/19/232758</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ubNcs4ulQ0w</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bootstrap学習、TOP画面レイアウト修正、faviconアイコン探し</t>
+    <rPh sb="9" eb="11">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bootstrapのタグ(中央寄せ等)</t>
+    <rPh sb="13" eb="16">
+      <t>チュウオウヨ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引き続きbootstrapを学びながらレイアウト修正中</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マナ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -25644,6 +25730,1003 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1512014-7E55-48A5-A156-301288989B5F}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M23" r:id="rId1" xr:uid="{ADC62980-5C48-4735-AA6A-ACDC44EB464F}"/>
+    <hyperlink ref="M24" r:id="rId2" xr:uid="{C9249F66-6150-4FD9-82BF-705E5BDD7AF5}"/>
+    <hyperlink ref="M25" r:id="rId3" xr:uid="{6745E4D8-FA4A-44B7-A7E2-AA2A75B7B7CC}"/>
+    <hyperlink ref="M26" r:id="rId4" xr:uid="{1375FFC0-FF0A-4033-87C5-AD8C7506526B}"/>
+    <hyperlink ref="M27" r:id="rId5" xr:uid="{221CCEA3-DC64-465C-8D2C-652204AF48B9}"/>
+    <hyperlink ref="M28" r:id="rId6" xr:uid="{A985AB50-20FB-433A-8085-1FFB92654568}"/>
+    <hyperlink ref="M29" r:id="rId7" xr:uid="{30BD0659-38D6-46BE-85BF-2A12A7DAB71A}"/>
+    <hyperlink ref="M30" r:id="rId8" xr:uid="{C0D06444-2319-46F2-ACE8-3E64CB4F7822}"/>
+    <hyperlink ref="M31" r:id="rId9" xr:uid="{BDD9903B-7052-4881-AE16-CD2CCE13BBAC}"/>
+    <hyperlink ref="M32" r:id="rId10" xr:uid="{D823648C-8BA7-451D-A927-09EAE57FD23A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A138BB4-7EF5-4466-A2D0-CDE54D22AE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB81608F-8A2D-46D9-9DB3-385630144408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="30" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="31" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <sheet name="8-9" sheetId="29" r:id="rId29"/>
     <sheet name="8-10" sheetId="31" r:id="rId30"/>
     <sheet name="8-11" sheetId="32" r:id="rId31"/>
+    <sheet name="8-12" sheetId="33" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="202">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1661,6 +1662,70 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Bootstrap学習、TOP画面レイアウト修正、ヘッダー部品化、ベースファイル作成</t>
+    <rPh sb="9" eb="11">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ブヒンカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベースファイルによるコードの部品化</t>
+    <rPh sb="14" eb="17">
+      <t>ブヒンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/miriwo/items/7c256af2959ef5b08b3b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://cly7796.net/blog/php/to-a-common-layout-in-blade-template-of-laravel/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://getbootstrap.jp/docs/5.3/components/navbar/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>引き続きbootstrapを学びながらレイアウト修正中
+コードの部品化については完了</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マナ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ブヒンカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -26727,6 +26792,962 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0710C7B-494D-4CF5-BC4B-7BE46A9F7D6D}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K34" r:id="rId1" xr:uid="{0807D7F9-DDC3-492F-889A-F36E4A060725}"/>
+    <hyperlink ref="K35" r:id="rId2" xr:uid="{013514CC-E36E-4495-AC2C-CFB6260F3527}"/>
+    <hyperlink ref="K36" r:id="rId3" xr:uid="{EB886ECE-6DBC-4690-B2B8-5434145AE0E7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB81608F-8A2D-46D9-9DB3-385630144408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB79B64-FAC2-4F7D-8159-7E05B90699D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="31" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="32" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -45,6 +45,7 @@
     <sheet name="8-10" sheetId="31" r:id="rId30"/>
     <sheet name="8-11" sheetId="32" r:id="rId31"/>
     <sheet name="8-12" sheetId="33" r:id="rId32"/>
+    <sheet name="8-13" sheetId="34" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3031" uniqueCount="204">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1726,6 +1727,45 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>metaタグをアノテーションで部品化、検索画面作成</t>
+    <rPh sb="15" eb="18">
+      <t>ブヒンカ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ケンサクガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引き続きbootstrapを学びながらレイアウト修正中
+metaタグの部品化については完了</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マナ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ブヒンカ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -27748,6 +27788,959 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BCF6A8-6D74-4012-8D66-6C641AE2A83A}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K34" r:id="rId1" xr:uid="{312B91B2-E888-4A63-B6F8-EB8BB5F1C054}"/>
+    <hyperlink ref="K35" r:id="rId2" xr:uid="{BCF815BE-43BF-461B-9369-6B057413E581}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB79B64-FAC2-4F7D-8159-7E05B90699D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958F3786-EF8D-4C7A-960A-7B4027ADE7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="32" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="33" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <sheet name="8-11" sheetId="32" r:id="rId31"/>
     <sheet name="8-12" sheetId="33" r:id="rId32"/>
     <sheet name="8-13" sheetId="34" r:id="rId33"/>
+    <sheet name="8-14" sheetId="35" r:id="rId34"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3031" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3112" uniqueCount="206">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1766,6 +1767,36 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t xml:space="preserve">HTMLスキル検索結果画面を作成中
+</t>
+    <rPh sb="7" eb="13">
+      <t>ケンサクケッカガメン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTMLスキル検索結果画面作成中</t>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -28741,6 +28772,969 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CDCF50-94E7-4073-8BC1-5C079BEFD9C1}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K34" r:id="rId1" xr:uid="{3F0606A1-587C-48AC-97A7-5E58BB54843B}"/>
+    <hyperlink ref="K35" r:id="rId2" xr:uid="{26805392-674E-44EE-B774-9B112C9CD040}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958F3786-EF8D-4C7A-960A-7B4027ADE7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80B211-6C7D-43D5-9166-5976E51A6922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="33" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="23" activeTab="34" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -47,6 +47,7 @@
     <sheet name="8-12" sheetId="33" r:id="rId32"/>
     <sheet name="8-13" sheetId="34" r:id="rId33"/>
     <sheet name="8-14" sheetId="35" r:id="rId34"/>
+    <sheet name="8-15" sheetId="36" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3112" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="211">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1797,6 +1798,83 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>HTMLスキル検索結果画面、HTMLスキル詳細画面作成</t>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://gyas.co.jp/knowledge_blog/laravel-route-modelbinding/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/shizen-shin/items/24d22265db47d7fb3c3d</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/Powerweb/items/497a990e1a0e60de5d15</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HTMLスキル検索結果画面、HTMLスキル詳細画面作成。
+処理の作成は完了。
+(更新、削除機能については未着手)
+</t>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ミチャクシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -29735,6 +29813,1012 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6FF5E-0A25-4D27-9A2F-A750039A4021}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M15" r:id="rId1" xr:uid="{17C157A7-C206-49EC-99CB-480599BC7ACA}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{7D217B12-D3E3-4568-AD58-3C0ED253DACB}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{FA8EAC83-0F21-485A-9A06-9A197E7640BA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80B211-6C7D-43D5-9166-5976E51A6922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310DB1A0-8E29-4F99-9785-E85D7D70C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="23" activeTab="34" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="24" activeTab="35" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -48,6 +48,7 @@
     <sheet name="8-13" sheetId="34" r:id="rId33"/>
     <sheet name="8-14" sheetId="35" r:id="rId34"/>
     <sheet name="8-15" sheetId="36" r:id="rId35"/>
+    <sheet name="8-16" sheetId="37" r:id="rId36"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="213">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1875,6 +1876,55 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>更新処理がタイムアウトを起こすため確認できない</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンショリ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HTMLスキル更新、削除機能作成中
+(更新機能に関してはタイムアウトが起こるため原因確認中)
+</t>
+    <rPh sb="7" eb="9">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>コウシンキノウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -30819,6 +30869,979 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0F0789-80DD-4D6D-BAEF-8354D45500C6}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310DB1A0-8E29-4F99-9785-E85D7D70C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC8CC8D-245F-4610-B9AD-3EE9086B40C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="24" activeTab="35" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="25" activeTab="36" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -49,6 +49,7 @@
     <sheet name="8-14" sheetId="35" r:id="rId34"/>
     <sheet name="8-15" sheetId="36" r:id="rId35"/>
     <sheet name="8-16" sheetId="37" r:id="rId36"/>
+    <sheet name="8-17" sheetId="38" r:id="rId37"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3303" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3375" uniqueCount="218">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1925,6 +1926,70 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>昨日同様更新処理がタイムアウトを起こすため確認できない</t>
+    <rPh sb="0" eb="2">
+      <t>サクジツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>コウシンショリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新処理時のタイムアウト原因調査</t>
+    <rPh sb="0" eb="5">
+      <t>コウシンショリジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/free-honda/items/64981ce8cfa72a9d1173</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://re-vite.com/blog/blog-855/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+昨日のタイムアウトが起こるための原因確認中。現在も解消できず。
+</t>
+    <rPh sb="1" eb="3">
+      <t>サクジツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -31842,6 +31907,950 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4377A38-767C-4E3A-9F5D-249D85B06EC0}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K36" r:id="rId1" xr:uid="{E22C4A64-966F-4B75-9349-69E4C53B770B}"/>
+    <hyperlink ref="K37" r:id="rId2" xr:uid="{31795104-6A23-445E-A255-16D252C5B0ED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC8CC8D-245F-4610-B9AD-3EE9086B40C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0B8826-6F05-4DDA-808E-F61023C3D150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="25" activeTab="36" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="37" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -50,6 +50,7 @@
     <sheet name="8-15" sheetId="36" r:id="rId35"/>
     <sheet name="8-16" sheetId="37" r:id="rId36"/>
     <sheet name="8-17" sheetId="38" r:id="rId37"/>
+    <sheet name="8-18" sheetId="39" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3375" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="223">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -1990,6 +1991,53 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://qiita.com/sc_tsuchiya/items/d68436f374fcd3531cf6</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/tatsu_nomad/items/2be8f9b6fd4730c7e419</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/mitate_gengaku/articles/docker-builder-prune</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/rainbowta/items/f467c3783b845271eeda</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+昨日のタイムアウトが起こるための原因確認中。
+キャッシュの削除を試すも現在も解消できず。
+</t>
+    <rPh sb="1" eb="3">
+      <t>サクジツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -32851,6 +32899,966 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA1819-D690-482C-8C2A-B0A3D11E6489}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K36" r:id="rId1" xr:uid="{D4C7B638-30D1-4F65-B6FB-562D0C2364F3}"/>
+    <hyperlink ref="K37" r:id="rId2" xr:uid="{82109E1F-F51F-446D-B3B0-3BE00A6242AC}"/>
+    <hyperlink ref="K38" r:id="rId3" xr:uid="{94C7241E-0984-43B1-93B8-6A801CA16ED9}"/>
+    <hyperlink ref="K39" r:id="rId4" xr:uid="{E13A8684-C7D6-44E3-8227-175492EEE988}"/>
+    <hyperlink ref="K40" r:id="rId5" xr:uid="{62AF147A-F66B-450E-9FD3-7E13D65021F3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0B8826-6F05-4DDA-808E-F61023C3D150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C26CC5-7354-40A2-839D-CD6C97B6DFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="37" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="27" activeTab="38" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -51,6 +51,7 @@
     <sheet name="8-16" sheetId="37" r:id="rId36"/>
     <sheet name="8-17" sheetId="38" r:id="rId37"/>
     <sheet name="8-18" sheetId="39" r:id="rId38"/>
+    <sheet name="8-19" sheetId="40" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="230">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2038,6 +2039,107 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>タイムアウトの原因がわからない</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://syuntech.net/php/laravel/docker-windows/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/mako0104/questions/f655206741c14a77ada8</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/conbrio/articles/fcf937c4049132</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/bm0/items/9db96258739c7a4c277b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://dojo.docker.jp/t/topic/52/2</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">引き続きタイムアウトが起こるための原因確認中。
+コントローラーでリクエストを受け取った直後にデバック(dd($request-&gt;all());)を入れてみたところ。
+リクエスト自体は正常に完了しているが、リクエストを受け取った後の更新処理($html-&gt;date = Carbon::today()-&gt;format('Y-m-d');以降)
+にデバック(dd($request-&gt;all());)を入れるとタイムアウトするので明日はそのあたりを調べる予定。
+</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>チョクゴ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>アス</t>
+    </rPh>
+    <rPh sb="222" eb="223">
+      <t>シラ</t>
+    </rPh>
+    <rPh sb="225" eb="227">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -33859,6 +33961,985 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05AFB0-7C88-4CE5-8272-8F6FC78061E4}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K32" r:id="rId1" xr:uid="{0F591583-3266-43CE-8EC5-EB9272435DB6}"/>
+    <hyperlink ref="K33" r:id="rId2" xr:uid="{A1EAE872-FC2A-4014-9D2E-36CA224BCDAD}"/>
+    <hyperlink ref="K34" r:id="rId3" xr:uid="{2A1CD00A-B4AC-4712-A0A9-25A88FC5D1AD}"/>
+    <hyperlink ref="K35" r:id="rId4" xr:uid="{EEEC4D75-349E-483C-8D24-10EF5A2D8B13}"/>
+    <hyperlink ref="K36" r:id="rId5" xr:uid="{4BFB7660-E21F-444B-A272-91866BD546F8}"/>
+    <hyperlink ref="K37" r:id="rId6" xr:uid="{3F9822E8-098D-4FE6-8314-0DF88B632582}"/>
+    <hyperlink ref="K38" r:id="rId7" xr:uid="{B474A163-A9BA-4779-B430-CA43585DDC87}"/>
+    <hyperlink ref="K39" r:id="rId8" xr:uid="{B3E3A567-9E1D-4E9E-8B49-0AFA7084D06D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C26CC5-7354-40A2-839D-CD6C97B6DFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ECB268-5D98-4AF2-B8DE-4B3EA498C872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="27" activeTab="38" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="39" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -52,6 +52,7 @@
     <sheet name="8-17" sheetId="38" r:id="rId37"/>
     <sheet name="8-18" sheetId="39" r:id="rId38"/>
     <sheet name="8-19" sheetId="40" r:id="rId39"/>
+    <sheet name="8-20" sheetId="41" r:id="rId40"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3610" uniqueCount="233">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2140,6 +2141,82 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>なし(過去のララベル課題のpdf(6-3,4,5)を見返した)</t>
+    <rPh sb="3" eb="5">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ミカエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー解決方法</t>
+    <rPh sb="3" eb="7">
+      <t>カイケツホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">引き続きタイムアウトが起こるための原因確認。
+エラーの原因が判明した。
+$html-&gt;date = Carbon::today()-&gt;format('Y-m-d');で日付取得しているがCarbonクラスのuse宣言が抜けていたため
+処理が正常に動かなかった。Carbonクラスのuse宣言を追記することで解決。
+</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハンメイ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -35901,6 +35978,955 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339F0ADB-EC8A-4414-B29C-BB02190C92C3}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ECB268-5D98-4AF2-B8DE-4B3EA498C872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A9C1F9-43B7-4D14-9334-9FF2CC86C5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="39" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="30" activeTab="40" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -53,6 +53,7 @@
     <sheet name="8-18" sheetId="39" r:id="rId38"/>
     <sheet name="8-19" sheetId="40" r:id="rId39"/>
     <sheet name="8-20" sheetId="41" r:id="rId40"/>
+    <sheet name="8-21" sheetId="42" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3610" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="235">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2217,6 +2218,29 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>バリデーション作成</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリデーションを作成し、想定通りのバリデーションが表示されることを確認した。</t>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ソウテイドオ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -36927,6 +36951,955 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C89191-B9A7-4B58-90DE-3BA1AC866D66}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A9C1F9-43B7-4D14-9334-9FF2CC86C5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F68F949-EF5C-46F1-9572-432251AA55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="30" activeTab="40" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="41" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -54,6 +54,7 @@
     <sheet name="8-19" sheetId="40" r:id="rId39"/>
     <sheet name="8-20" sheetId="41" r:id="rId40"/>
     <sheet name="8-21" sheetId="42" r:id="rId41"/>
+    <sheet name="8-22" sheetId="43" r:id="rId42"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="247">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2241,6 +2242,121 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>javascript,jquery復習</t>
+    <rPh sb="17" eb="19">
+      <t>フクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>javascript,jquery復習、更新、削除追加完了画面作成(update,delete,create_complete.blade)</t>
+    <rPh sb="17" eb="19">
+      <t>フクシュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンタグへのリンク付け</t>
+    <rPh sb="10" eb="11">
+      <t>ヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>javascript,jqueryの復習</t>
+    <rPh sb="18" eb="20">
+      <t>フクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ajaxとapiの機能を本課題の中でどのように実装するかイメージわかない</t>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/k-tabuchi/items/5db77428ff5d912e8624</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://hajimete.org/jquery-ajax-data-fetch</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/neogym/items/0b89daa73ebb2a1d27d5</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/4649rixxxz/items/d31ecb33fcba1bffcb90</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ajaxを学ぶためにjavascriptの復習をした。
+また完了画面を作成し、戻るボタンも修正した。</t>
+    <rPh sb="5" eb="6">
+      <t>マナ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フクシュウ</t>
+    </rPh>
+    <rPh sb="30" eb="34">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -37900,6 +38016,991 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D961EB-8F82-44AB-8377-3106023C56AF}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="K27" r:id="rId1" xr:uid="{5F600958-762D-45BB-9EC6-E5B73973608D}"/>
+    <hyperlink ref="K28" r:id="rId2" xr:uid="{23A91A0A-EFB7-462F-8A57-689CFD7DF39D}"/>
+    <hyperlink ref="K26" r:id="rId3" xr:uid="{F678E05B-C9B0-4377-9E9D-9E22A6B7D014}"/>
+    <hyperlink ref="K29" r:id="rId4" xr:uid="{D1166C09-7140-433A-8858-FCAC90C4A1C4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F68F949-EF5C-46F1-9572-432251AA55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87CE560-A180-4DD9-ACE2-57E09E9A6F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="41" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="32" activeTab="42" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -55,6 +55,7 @@
     <sheet name="8-20" sheetId="41" r:id="rId40"/>
     <sheet name="8-21" sheetId="42" r:id="rId41"/>
     <sheet name="8-22" sheetId="43" r:id="rId42"/>
+    <sheet name="8-23" sheetId="44" r:id="rId43"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="255">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2357,6 +2358,69 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>本日はほとんど家にいなかったので資料の読み込みのみ</t>
+    <rPh sb="0" eb="2">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>javascript,jquery復習、ajax学習</t>
+    <rPh sb="17" eb="19">
+      <t>フクシュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ajaxの理解が不足しているのでさらに学習予定</t>
+    <rPh sb="5" eb="7">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://share.google/dvaQ2iLCy80XPredq</t>
+  </si>
+  <si>
+    <t>https://share.google/e4xltDyZEnfomInJk</t>
+  </si>
+  <si>
+    <t>https://share.google/djGXKMHR1Kb6kTbiN</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://share.google/2KCinN4oy2jKCppTz</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://share.google/WUbDz3FrGQurHxoMY</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -39001,6 +39065,979 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6768BE0-819D-489F-813B-79AE506BF05C}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M13" r:id="rId1" xr:uid="{D7F47EB3-F65E-4731-ADB4-BA896E9B1A3B}"/>
+    <hyperlink ref="M12" r:id="rId2" xr:uid="{9D065773-7F64-4FF7-936B-1F9DE44F77A6}"/>
+    <hyperlink ref="M14" r:id="rId3" xr:uid="{723B641C-A458-48AA-B064-2CF4D799A06D}"/>
+    <hyperlink ref="M15" r:id="rId4" xr:uid="{96DE6773-EAC5-46AA-88ED-1BEF63EAB528}"/>
+    <hyperlink ref="M16" r:id="rId5" xr:uid="{17C26DF4-6436-4259-AAF6-751B36988B3E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87CE560-A180-4DD9-ACE2-57E09E9A6F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FA84A1-B72F-47B6-B782-3E201B57E5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="32" activeTab="42" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="33" activeTab="43" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -56,6 +56,7 @@
     <sheet name="8-21" sheetId="42" r:id="rId41"/>
     <sheet name="8-22" sheetId="43" r:id="rId42"/>
     <sheet name="8-23" sheetId="44" r:id="rId43"/>
+    <sheet name="8-24" sheetId="45" r:id="rId44"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="265">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2421,6 +2422,81 @@
     <t>https://share.google/WUbDz3FrGQurHxoMY</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>戻るボタン設置</t>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハンバーガーメニュー作成</t>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://katsu-coach.com/programming/bootstrap-10/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://getbootstrap.jp/docs/5.3/utilities/position/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/kaishigaki/articles/216ea780916bdf</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://sakuweb.liruu.com/bootstrap/bootstrap-c19/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/ikadatic/items/c033ab1244f53a895496</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/hmmrjn/items/6f5fd65ab8c58cd7a6d6</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>認証機能実装</t>
+    <rPh sb="0" eb="4">
+      <t>ニンショウキノウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戻るボタン設置、ハンバーガーメニュー作成が完了
+認証機能実装についてはパスワードリセットと権限分けを除き完了
+設計書は修正できてません。</t>
+    <rPh sb="21" eb="23">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>ケンゲンワ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -40038,6 +40114,1014 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53562B77-777F-46DF-B9F6-984568C5E4CE}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{8A073341-FE24-4658-8D3E-D5D9EAA8B9ED}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{47501AB6-C6D3-4939-B440-8357E559C291}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{0C157815-9F30-4ED2-8569-A4559F3DAA20}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{09D8F3A5-7253-47C5-BE75-99DACF0DB0E7}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{E028E025-29CC-4D74-A2CE-01430B8C87F0}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{D30CE822-6738-4D18-AE22-CDE3F8C28BB9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <dimension ref="B2:N58"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FA84A1-B72F-47B6-B782-3E201B57E5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCBF030-86F0-4E75-A5F4-853DA54F6748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="33" activeTab="43" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="34" activeTab="44" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -57,6 +57,7 @@
     <sheet name="8-22" sheetId="43" r:id="rId42"/>
     <sheet name="8-23" sheetId="44" r:id="rId43"/>
     <sheet name="8-24" sheetId="45" r:id="rId44"/>
+    <sheet name="8-25" sheetId="46" r:id="rId45"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="272">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2497,6 +2498,68 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>postmanインストール、パスワードリセットapi用のコントローラーとリクエストファイル作成</t>
+    <rPh sb="21" eb="22">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだapi作成方法を全体的に理解できていない</t>
+    <rPh sb="5" eb="9">
+      <t>サクセイホウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/miya1221/items/868a047950f04cd5e80d</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/ucan-lab/items/c72f1fe32543d3e8add3</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/EasyCoder/items/32c4e207255fab6338a8</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>apiでパスワードリセット機能を作成するためコントローラー(/ForgotPasswordController.php)とリクエスト(ForgotPasswordRequest.php)ファイル作成及び
+apiをテストするたっめにpostmanのインストールも実施。Postmanを用いてのテストは未実施</t>
+    <rPh sb="13" eb="15">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="97" eb="100">
+      <t>サクセイオヨ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="149" eb="152">
+      <t>ミジッシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2980,6 +3043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1B8595-23C2-4398-862A-00FDB4B5CF1D}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4008,6 +4072,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18A5555-581D-493E-9321-B2E41B7341F7}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4994,6 +5059,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D771B576-707B-420D-B48A-5E4666DBBB32}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5971,6 +6037,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFCD5765-144B-40E5-B41C-0393751F5730}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6946,6 +7013,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B0258B-E197-453F-B980-F627CB34A610}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -7911,6 +7979,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EF2740-4CC9-45C8-9F66-2184D0AB0598}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8885,6 +8954,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5303352D-BD82-4A67-A3AE-1A0E3F13FD3C}">
+  <sheetPr codeName="Sheet15"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -9920,6 +9990,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846D479F-EBD6-4BA3-A970-B803910FCE79}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -10950,6 +11021,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785E0503-D0BA-4AE0-810D-7B9F6B0A99B3}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -11940,6 +12012,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA425A6B-6E26-49F5-9668-3980AFA1BB76}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12914,6 +12987,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922FE6F0-4833-4FD0-AC1D-65611CE7E123}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13897,6 +13971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC5DB89-E601-43E1-B739-06DB61B103F2}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -14871,6 +14946,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C17881-DAFD-4C84-A17F-55BBEAD03995}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15853,6 +15929,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F709F27A-B438-425D-9CE5-4433D56D41EB}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -16881,6 +16958,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F8F46C-F54E-4291-B263-30F09581E207}">
+  <sheetPr codeName="Sheet22"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -17910,6 +17988,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678713E6-01EC-4AF8-B85B-EFBD12D6B70F}">
+  <sheetPr codeName="Sheet23"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -18866,6 +18945,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334ED2BD-C64B-41B3-9E46-E393C83DCE0D}">
+  <sheetPr codeName="Sheet24"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -19824,6 +19904,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0076AB3-51EE-48BC-AEC0-7BB9E3567B7B}">
+  <sheetPr codeName="Sheet25"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -20774,6 +20855,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B0924B-EDEF-4DF7-8455-9FD768646ACB}">
+  <sheetPr codeName="Sheet26"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -21741,6 +21823,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A3349F-C52E-4B58-A37E-71036D68DB5F}">
+  <sheetPr codeName="Sheet27"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -22696,6 +22779,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295EA6C7-41C0-4647-800C-73142E5C7312}">
+  <sheetPr codeName="Sheet28"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -23655,6 +23739,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDD0B73-E798-4DEF-9280-3A586EB1328D}">
+  <sheetPr codeName="Sheet29"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -24651,6 +24736,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -25617,6 +25703,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA70BF8E-E61E-4DD4-B092-05B5B84C146C}">
+  <sheetPr codeName="Sheet30"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -26568,6 +26655,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1512014-7E55-48A5-A156-301288989B5F}">
+  <sheetPr codeName="Sheet31"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27565,6 +27653,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0710C7B-494D-4CF5-BC4B-7BE46A9F7D6D}">
+  <sheetPr codeName="Sheet32"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -28521,6 +28610,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BCF6A8-6D74-4012-8D66-6C641AE2A83A}">
+  <sheetPr codeName="Sheet33"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -29474,6 +29564,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CDCF50-94E7-4073-8BC1-5C079BEFD9C1}">
+  <sheetPr codeName="Sheet34"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -30437,6 +30528,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6FF5E-0A25-4D27-9A2F-A750039A4021}">
+  <sheetPr codeName="Sheet35"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -31443,6 +31535,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0F0789-80DD-4D6D-BAEF-8354D45500C6}">
+  <sheetPr codeName="Sheet36"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -32416,6 +32509,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4377A38-767C-4E3A-9F5D-249D85B06EC0}">
+  <sheetPr codeName="Sheet37"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -33360,6 +33454,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA1819-D690-482C-8C2A-B0A3D11E6489}">
+  <sheetPr codeName="Sheet38"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -34320,6 +34415,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05AFB0-7C88-4CE5-8272-8F6FC78061E4}">
+  <sheetPr codeName="Sheet39"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -35299,6 +35395,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -36260,6 +36357,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339F0ADB-EC8A-4414-B29C-BB02190C92C3}">
+  <sheetPr codeName="Sheet40"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37209,6 +37307,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C89191-B9A7-4B58-90DE-3BA1AC866D66}">
+  <sheetPr codeName="Sheet41"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -38158,6 +38257,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D961EB-8F82-44AB-8377-3106023C56AF}">
+  <sheetPr codeName="Sheet42"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -39143,6 +39243,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6768BE0-819D-489F-813B-79AE506BF05C}">
+  <sheetPr codeName="Sheet43"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -40116,6 +40217,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53562B77-777F-46DF-B9F6-984568C5E4CE}">
+  <sheetPr codeName="Sheet44"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -41122,8 +41224,994 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AC2003-9C45-4AB3-BED1-87587F05F0E5}">
+  <sheetPr codeName="Sheet45"/>
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{874417D0-EA7B-4245-8500-C8B71E768239}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{DA7B9483-2580-41F0-B6F5-194709095BE3}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{E620ECFA-D74A-4CCF-B92D-9B83FCB4A309}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{B2A94603-4625-4F0B-9D25-09B18A785B04}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{7130C53A-83D8-436C-AB53-CB3FCF81D52E}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{28E2A037-2E72-4270-9BB1-C103682AEC13}"/>
+    <hyperlink ref="K35" r:id="rId7" xr:uid="{3F29F36F-65AE-4EAB-B658-0E440B68158A}"/>
+    <hyperlink ref="K36" r:id="rId8" xr:uid="{7AC9A6B5-DA16-45C4-9539-386F5AAEA2CB}"/>
+    <hyperlink ref="K37" r:id="rId9" xr:uid="{3029B4C6-1641-4FB5-AB9F-8F30CAB4155C}"/>
+    <hyperlink ref="K38" r:id="rId10" xr:uid="{2C09844C-0624-4201-95F4-63DA773F2C10}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -42098,6 +43186,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56A0045-9D53-4CC6-A5D6-D0144024C4B8}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -43068,6 +44157,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D6DC6F-267C-4F17-A216-7F3B96758D43}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -44047,6 +45137,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5E7C19-79D0-44D8-B74F-21C9B37B6919}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -45045,6 +46136,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A6C636-4572-4F93-A5EA-E88774DAB386}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCBF030-86F0-4E75-A5F4-853DA54F6748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD65ABEF-6BE1-4D11-9340-9B63577B29E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="34" activeTab="44" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="35" activeTab="45" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -58,6 +58,7 @@
     <sheet name="8-23" sheetId="44" r:id="rId43"/>
     <sheet name="8-24" sheetId="45" r:id="rId44"/>
     <sheet name="8-25" sheetId="46" r:id="rId45"/>
+    <sheet name="8-26" sheetId="47" r:id="rId46"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -84,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="279">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2560,6 +2561,83 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>postmanでapi送信確認</t>
+    <rPh sb="11" eb="15">
+      <t>ソウシンカクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/zou-g/items/fe7e640d7e376aaf674e</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/miriwo/items/25767d0956ea2cdc6f21</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.echoapi.jp/blog/untitled-34/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>api送信確認ができない。</t>
+    <rPh sb="3" eb="5">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
+Postmanの使用方法の理解、apiへの理解が全般的に不足しているため学習して解決していく予定。</t>
+    <rPh sb="0" eb="4">
+      <t>サクジツサクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="73" eb="77">
+      <t>シヨウホウホウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="89" eb="92">
+      <t>ゼンパンテキ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -42209,6 +42287,1009 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBDB166-6101-47CA-80A3-5991486736B1}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{127C52AB-8F54-4CB4-930F-537CB5B24888}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{90D152F9-C630-4A3A-85C3-BC413E33EDF4}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{071F3FF9-0AD9-4BFE-817A-EE01411AF02A}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{20847A6C-99F3-4760-9C93-8876CC2F2B0F}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{9FBBD212-1082-4928-A229-0BF9A7EDDC25}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{2ECB9528-2279-476B-826C-52D747B85E6F}"/>
+    <hyperlink ref="K34" r:id="rId7" xr:uid="{48EA548D-86DE-473F-A73C-3853E5738800}"/>
+    <hyperlink ref="K35" r:id="rId8" xr:uid="{F24B6437-1E3D-4746-96E3-49A44790DAC5}"/>
+    <hyperlink ref="K36" r:id="rId9" xr:uid="{91619E24-965D-478B-9168-A68665DF7AB5}"/>
+    <hyperlink ref="K37" r:id="rId10" xr:uid="{DE5C55A2-66A6-4C47-A28F-B096781FC84B}"/>
+    <hyperlink ref="K38" r:id="rId11" xr:uid="{D5CFD281-0C2B-44DF-B013-CDE6E8DC6DF1}"/>
+    <hyperlink ref="K39" r:id="rId12" xr:uid="{D86246C5-29CE-4F90-9E07-D5686C7B1C73}"/>
+    <hyperlink ref="K40" r:id="rId13" xr:uid="{73BDF172-03B6-4519-B1F6-03AA13A6336E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <sheetPr codeName="Sheet5"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD65ABEF-6BE1-4D11-9340-9B63577B29E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645E2A2F-DD1C-4E00-A2FD-4AE54C48C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="35" activeTab="45" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="36" activeTab="46" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -59,6 +59,7 @@
     <sheet name="8-24" sheetId="45" r:id="rId44"/>
     <sheet name="8-25" sheetId="46" r:id="rId45"/>
     <sheet name="8-26" sheetId="47" r:id="rId46"/>
+    <sheet name="8-27" sheetId="48" r:id="rId47"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="284">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2638,6 +2639,81 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>https://apidog.com/jp/blog/how-to-send-json-with-postman/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://readouble.com/laravel/6.x/ja/passwords.html</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/rikako_hira/items/4626090769f4023d4107</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://skillhub.jp/courses/581/lessons/4549</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>引き続き昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
+Gitの履歴を過去( “20260824-画面等作成”)にさかのぼって下記コマンドを打つとartisanできた。
+ディレクトリを比較してみたが最新版と差異がないためコントローラーの中身がおかしい可能性があるので確認する。
+php artisan make:request Api/Auth/ForgotPasswordRequest
+php artisan make:controller -i Api/Auth/ForgotPasswordController</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>サクジツサクセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="140" eb="143">
+      <t>サイシンバン</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="166" eb="169">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -43290,6 +43366,1013 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715C72A0-4896-4247-B188-D05AD34E38C3}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{58B43F36-B281-4BEC-BF53-A2A57A48F50A}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{EBDE1810-5F40-45CA-8F8D-16D979340D89}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{DB07D43B-BA2F-4B03-9A82-2A6C65B2EF2D}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{314BDC1B-885D-4EF2-90B4-3E6DBD7187C6}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{454208C9-DBEB-427D-815F-C2A2533A322E}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{64FA2FC7-7A61-4C06-8C5D-E38209D17D33}"/>
+    <hyperlink ref="K33" r:id="rId7" display="https://skillhub.jp/courses/581/lessons/4549" xr:uid="{BF67BB14-C2EF-4364-84E4-A5DD1698391D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <sheetPr codeName="Sheet5"/>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FA84A1-B72F-47B6-B782-3E201B57E5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B884665-3357-4FE9-8D12-3F20B34FBCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="33" activeTab="43" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="37" activeTab="47" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -57,6 +57,10 @@
     <sheet name="8-22" sheetId="43" r:id="rId42"/>
     <sheet name="8-23" sheetId="44" r:id="rId43"/>
     <sheet name="8-24" sheetId="45" r:id="rId44"/>
+    <sheet name="8-25" sheetId="46" r:id="rId45"/>
+    <sheet name="8-26" sheetId="47" r:id="rId46"/>
+    <sheet name="8-27" sheetId="48" r:id="rId47"/>
+    <sheet name="8-28" sheetId="49" r:id="rId48"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -83,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="288">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2497,6 +2501,264 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>postmanインストール、パスワードリセットapi用のコントローラーとリクエストファイル作成</t>
+    <rPh sb="21" eb="22">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まだapi作成方法を全体的に理解できていない</t>
+    <rPh sb="5" eb="9">
+      <t>サクセイホウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ゼンタイテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/miya1221/items/868a047950f04cd5e80d</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/ucan-lab/items/c72f1fe32543d3e8add3</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/EasyCoder/items/32c4e207255fab6338a8</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>apiでパスワードリセット機能を作成するためコントローラー(/ForgotPasswordController.php)とリクエスト(ForgotPasswordRequest.php)ファイル作成及び
+apiをテストするたっめにpostmanのインストールも実施。Postmanを用いてのテストは未実施</t>
+    <rPh sb="13" eb="15">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="97" eb="100">
+      <t>サクセイオヨ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="149" eb="152">
+      <t>ミジッシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>postmanでapi送信確認</t>
+    <rPh sb="11" eb="15">
+      <t>ソウシンカクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/zou-g/items/fe7e640d7e376aaf674e</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/miriwo/items/25767d0956ea2cdc6f21</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://www.echoapi.jp/blog/untitled-34/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>api送信確認ができない。</t>
+    <rPh sb="3" eb="5">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
+Postmanの使用方法の理解、apiへの理解が全般的に不足しているため学習して解決していく予定。</t>
+    <rPh sb="0" eb="4">
+      <t>サクジツサクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="73" eb="77">
+      <t>シヨウホウホウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="89" eb="92">
+      <t>ゼンパンテキ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://apidog.com/jp/blog/how-to-send-json-with-postman/</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://readouble.com/laravel/6.x/ja/passwords.html</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://qiita.com/rikako_hira/items/4626090769f4023d4107</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://skillhub.jp/courses/581/lessons/4549</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>引き続き昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
+Gitの履歴を過去( “20260824-画面等作成”)にさかのぼって下記コマンドを打つとartisanできた。
+ディレクトリを比較してみたが最新版と差異がないためコントローラーの中身がおかしい可能性があるので確認する。
+php artisan make:request Api/Auth/ForgotPasswordRequest
+php artisan make:controller -i Api/Auth/ForgotPasswordController</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>サクジツサクセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="140" eb="143">
+      <t>サイシンバン</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="166" eb="169">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>権限分け</t>
+    <rPh sb="0" eb="2">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロールによる権限分け</t>
+    <rPh sb="6" eb="8">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://qiita.com/ryuseino/items/ef82fb04d1347634f71c</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>apiはいったん飛ばして権限分けを実施。
+権限分けについては完了</t>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ケンゲンワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ケンゲンワ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2980,6 +3242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1B8595-23C2-4398-862A-00FDB4B5CF1D}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4008,6 +4271,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18A5555-581D-493E-9321-B2E41B7341F7}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4994,6 +5258,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D771B576-707B-420D-B48A-5E4666DBBB32}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5971,6 +6236,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFCD5765-144B-40E5-B41C-0393751F5730}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6946,6 +7212,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B0258B-E197-453F-B980-F627CB34A610}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -7911,6 +8178,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EF2740-4CC9-45C8-9F66-2184D0AB0598}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8885,6 +9153,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5303352D-BD82-4A67-A3AE-1A0E3F13FD3C}">
+  <sheetPr codeName="Sheet15"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -9920,6 +10189,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846D479F-EBD6-4BA3-A970-B803910FCE79}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -10950,6 +11220,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785E0503-D0BA-4AE0-810D-7B9F6B0A99B3}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -11940,6 +12211,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA425A6B-6E26-49F5-9668-3980AFA1BB76}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12914,6 +13186,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922FE6F0-4833-4FD0-AC1D-65611CE7E123}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13897,6 +14170,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC5DB89-E601-43E1-B739-06DB61B103F2}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -14871,6 +15145,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C17881-DAFD-4C84-A17F-55BBEAD03995}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15853,6 +16128,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F709F27A-B438-425D-9CE5-4433D56D41EB}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -16881,6 +17157,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F8F46C-F54E-4291-B263-30F09581E207}">
+  <sheetPr codeName="Sheet22"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -17910,6 +18187,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678713E6-01EC-4AF8-B85B-EFBD12D6B70F}">
+  <sheetPr codeName="Sheet23"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -18866,6 +19144,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334ED2BD-C64B-41B3-9E46-E393C83DCE0D}">
+  <sheetPr codeName="Sheet24"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -19824,6 +20103,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0076AB3-51EE-48BC-AEC0-7BB9E3567B7B}">
+  <sheetPr codeName="Sheet25"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -20774,6 +21054,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B0924B-EDEF-4DF7-8455-9FD768646ACB}">
+  <sheetPr codeName="Sheet26"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -21741,6 +22022,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A3349F-C52E-4B58-A37E-71036D68DB5F}">
+  <sheetPr codeName="Sheet27"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -22696,6 +22978,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295EA6C7-41C0-4647-800C-73142E5C7312}">
+  <sheetPr codeName="Sheet28"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -23655,6 +23938,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDD0B73-E798-4DEF-9280-3A586EB1328D}">
+  <sheetPr codeName="Sheet29"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -24651,6 +24935,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -25617,6 +25902,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA70BF8E-E61E-4DD4-B092-05B5B84C146C}">
+  <sheetPr codeName="Sheet30"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -26568,6 +26854,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1512014-7E55-48A5-A156-301288989B5F}">
+  <sheetPr codeName="Sheet31"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27565,6 +27852,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0710C7B-494D-4CF5-BC4B-7BE46A9F7D6D}">
+  <sheetPr codeName="Sheet32"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -28521,6 +28809,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BCF6A8-6D74-4012-8D66-6C641AE2A83A}">
+  <sheetPr codeName="Sheet33"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -29474,6 +29763,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CDCF50-94E7-4073-8BC1-5C079BEFD9C1}">
+  <sheetPr codeName="Sheet34"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -30437,6 +30727,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6FF5E-0A25-4D27-9A2F-A750039A4021}">
+  <sheetPr codeName="Sheet35"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -31443,6 +31734,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0F0789-80DD-4D6D-BAEF-8354D45500C6}">
+  <sheetPr codeName="Sheet36"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -32416,6 +32708,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4377A38-767C-4E3A-9F5D-249D85B06EC0}">
+  <sheetPr codeName="Sheet37"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -33360,6 +33653,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA1819-D690-482C-8C2A-B0A3D11E6489}">
+  <sheetPr codeName="Sheet38"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -34320,6 +34614,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05AFB0-7C88-4CE5-8272-8F6FC78061E4}">
+  <sheetPr codeName="Sheet39"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -35299,6 +35594,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -36260,6 +36556,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339F0ADB-EC8A-4414-B29C-BB02190C92C3}">
+  <sheetPr codeName="Sheet40"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37209,6 +37506,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C89191-B9A7-4B58-90DE-3BA1AC866D66}">
+  <sheetPr codeName="Sheet41"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -38158,6 +38456,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D961EB-8F82-44AB-8377-3106023C56AF}">
+  <sheetPr codeName="Sheet42"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -39143,6 +39442,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6768BE0-819D-489F-813B-79AE506BF05C}">
+  <sheetPr codeName="Sheet43"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -40116,6 +40416,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53562B77-777F-46DF-B9F6-984568C5E4CE}">
+  <sheetPr codeName="Sheet44"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -41122,8 +41423,3969 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AC2003-9C45-4AB3-BED1-87587F05F0E5}">
+  <sheetPr codeName="Sheet45"/>
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{874417D0-EA7B-4245-8500-C8B71E768239}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{DA7B9483-2580-41F0-B6F5-194709095BE3}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{E620ECFA-D74A-4CCF-B92D-9B83FCB4A309}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{B2A94603-4625-4F0B-9D25-09B18A785B04}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{7130C53A-83D8-436C-AB53-CB3FCF81D52E}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{28E2A037-2E72-4270-9BB1-C103682AEC13}"/>
+    <hyperlink ref="K35" r:id="rId7" xr:uid="{3F29F36F-65AE-4EAB-B658-0E440B68158A}"/>
+    <hyperlink ref="K36" r:id="rId8" xr:uid="{7AC9A6B5-DA16-45C4-9539-386F5AAEA2CB}"/>
+    <hyperlink ref="K37" r:id="rId9" xr:uid="{3029B4C6-1641-4FB5-AB9F-8F30CAB4155C}"/>
+    <hyperlink ref="K38" r:id="rId10" xr:uid="{2C09844C-0624-4201-95F4-63DA773F2C10}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBDB166-6101-47CA-80A3-5991486736B1}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{127C52AB-8F54-4CB4-930F-537CB5B24888}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{90D152F9-C630-4A3A-85C3-BC413E33EDF4}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{071F3FF9-0AD9-4BFE-817A-EE01411AF02A}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{20847A6C-99F3-4760-9C93-8876CC2F2B0F}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{9FBBD212-1082-4928-A229-0BF9A7EDDC25}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{2ECB9528-2279-476B-826C-52D747B85E6F}"/>
+    <hyperlink ref="K34" r:id="rId7" xr:uid="{48EA548D-86DE-473F-A73C-3853E5738800}"/>
+    <hyperlink ref="K35" r:id="rId8" xr:uid="{F24B6437-1E3D-4746-96E3-49A44790DAC5}"/>
+    <hyperlink ref="K36" r:id="rId9" xr:uid="{91619E24-965D-478B-9168-A68665DF7AB5}"/>
+    <hyperlink ref="K37" r:id="rId10" xr:uid="{DE5C55A2-66A6-4C47-A28F-B096781FC84B}"/>
+    <hyperlink ref="K38" r:id="rId11" xr:uid="{D5CFD281-0C2B-44DF-B013-CDE6E8DC6DF1}"/>
+    <hyperlink ref="K39" r:id="rId12" xr:uid="{D86246C5-29CE-4F90-9E07-D5686C7B1C73}"/>
+    <hyperlink ref="K40" r:id="rId13" xr:uid="{73BDF172-03B6-4519-B1F6-03AA13A6336E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715C72A0-4896-4247-B188-D05AD34E38C3}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{58B43F36-B281-4BEC-BF53-A2A57A48F50A}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{EBDE1810-5F40-45CA-8F8D-16D979340D89}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{DB07D43B-BA2F-4B03-9A82-2A6C65B2EF2D}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{314BDC1B-885D-4EF2-90B4-3E6DBD7187C6}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{454208C9-DBEB-427D-815F-C2A2533A322E}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{64FA2FC7-7A61-4C06-8C5D-E38209D17D33}"/>
+    <hyperlink ref="K33" r:id="rId7" display="https://skillhub.jp/courses/581/lessons/4549" xr:uid="{BF67BB14-C2EF-4364-84E4-A5DD1698391D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AB0654-9A1F-4AF2-9885-EFB59B706C01}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M35" r:id="rId1" xr:uid="{A47DB830-8494-4BFD-B22D-3774735AE73D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -42098,6 +46360,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56A0045-9D53-4CC6-A5D6-D0144024C4B8}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -43068,6 +47331,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D6DC6F-267C-4F17-A216-7F3B96758D43}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -44047,6 +48311,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5E7C19-79D0-44D8-B74F-21C9B37B6919}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -45045,6 +49310,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A6C636-4572-4F93-A5EA-E88774DAB386}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B884665-3357-4FE9-8D12-3F20B34FBCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FA84A1-B72F-47B6-B782-3E201B57E5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="37" activeTab="47" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="33" activeTab="43" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -57,10 +57,6 @@
     <sheet name="8-22" sheetId="43" r:id="rId42"/>
     <sheet name="8-23" sheetId="44" r:id="rId43"/>
     <sheet name="8-24" sheetId="45" r:id="rId44"/>
-    <sheet name="8-25" sheetId="46" r:id="rId45"/>
-    <sheet name="8-26" sheetId="47" r:id="rId46"/>
-    <sheet name="8-27" sheetId="48" r:id="rId47"/>
-    <sheet name="8-28" sheetId="49" r:id="rId48"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -87,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="265">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2501,264 +2497,6 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>postmanインストール、パスワードリセットapi用のコントローラーとリクエストファイル作成</t>
-    <rPh sb="21" eb="22">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まだapi作成方法を全体的に理解できていない</t>
-    <rPh sb="5" eb="9">
-      <t>サクセイホウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ゼンタイテキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>リカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://qiita.com/miya1221/items/868a047950f04cd5e80d</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://qiita.com/ucan-lab/items/c72f1fe32543d3e8add3</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://qiita.com/EasyCoder/items/32c4e207255fab6338a8</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>apiでパスワードリセット機能を作成するためコントローラー(/ForgotPasswordController.php)とリクエスト(ForgotPasswordRequest.php)ファイル作成及び
-apiをテストするたっめにpostmanのインストールも実施。Postmanを用いてのテストは未実施</t>
-    <rPh sb="13" eb="15">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="97" eb="100">
-      <t>サクセイオヨ</t>
-    </rPh>
-    <rPh sb="130" eb="132">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="149" eb="152">
-      <t>ミジッシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>postmanでapi送信確認</t>
-    <rPh sb="11" eb="15">
-      <t>ソウシンカクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://zenn.dev/rasshii/books/laravel-ddd-and-clean-architecture/viewer/02-laravel-api-basics</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://qiita.com/zou-g/items/fe7e640d7e376aaf674e</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://qiita.com/miriwo/items/25767d0956ea2cdc6f21</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://www.echoapi.jp/blog/untitled-34/</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>api送信確認ができない。</t>
-    <rPh sb="3" eb="5">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
-Postmanの使用方法の理解、apiへの理解が全般的に不足しているため学習して解決していく予定。</t>
-    <rPh sb="0" eb="4">
-      <t>サクジツサクセイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="73" eb="77">
-      <t>シヨウホウホウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="89" eb="92">
-      <t>ゼンパンテキ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>フソク</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ガクシュウ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>カイケツ</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://apidog.com/jp/blog/how-to-send-json-with-postman/</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://readouble.com/laravel/6.x/ja/passwords.html</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://qiita.com/rikako_hira/items/4626090769f4023d4107</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>https://skillhub.jp/courses/581/lessons/4549</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>引き続き昨日作成したルーティングとコントローラーを利用してpostmanによるパスワードリセットメール送信を実施しているが送信できない。
-Gitの履歴を過去( “20260824-画面等作成”)にさかのぼって下記コマンドを打つとartisanできた。
-ディレクトリを比較してみたが最新版と差異がないためコントローラーの中身がおかしい可能性があるので確認する。
-php artisan make:request Api/Auth/ForgotPasswordRequest
-php artisan make:controller -i Api/Auth/ForgotPasswordController</t>
-    <rPh sb="0" eb="1">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>サクジツサクセイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>リレキ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="111" eb="112">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="140" eb="143">
-      <t>サイシンバン</t>
-    </rPh>
-    <rPh sb="144" eb="146">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>ナカミ</t>
-    </rPh>
-    <rPh sb="166" eb="169">
-      <t>カノウセイ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>権限分け</t>
-    <rPh sb="0" eb="2">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ロールによる権限分け</t>
-    <rPh sb="6" eb="8">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://qiita.com/ryuseino/items/ef82fb04d1347634f71c</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>apiはいったん飛ばして権限分けを実施。
-権限分けについては完了</t>
-    <rPh sb="8" eb="9">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ケンゲンワ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ケンゲンワ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
@@ -3242,7 +2980,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1B8595-23C2-4398-862A-00FDB4B5CF1D}">
-  <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4271,7 +4008,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18A5555-581D-493E-9321-B2E41B7341F7}">
-  <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5258,7 +4994,6 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D771B576-707B-420D-B48A-5E4666DBBB32}">
-  <sheetPr codeName="Sheet11"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6236,7 +5971,6 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFCD5765-144B-40E5-B41C-0393751F5730}">
-  <sheetPr codeName="Sheet12"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -7212,7 +6946,6 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B0258B-E197-453F-B980-F627CB34A610}">
-  <sheetPr codeName="Sheet13"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8178,7 +7911,6 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EF2740-4CC9-45C8-9F66-2184D0AB0598}">
-  <sheetPr codeName="Sheet14"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -9153,7 +8885,6 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5303352D-BD82-4A67-A3AE-1A0E3F13FD3C}">
-  <sheetPr codeName="Sheet15"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -10189,7 +9920,6 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846D479F-EBD6-4BA3-A970-B803910FCE79}">
-  <sheetPr codeName="Sheet16"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -11220,7 +10950,6 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785E0503-D0BA-4AE0-810D-7B9F6B0A99B3}">
-  <sheetPr codeName="Sheet17"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12211,7 +11940,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA425A6B-6E26-49F5-9668-3980AFA1BB76}">
-  <sheetPr codeName="Sheet18"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13186,7 +12914,6 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922FE6F0-4833-4FD0-AC1D-65611CE7E123}">
-  <sheetPr codeName="Sheet19"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -14170,7 +13897,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC5DB89-E601-43E1-B739-06DB61B103F2}">
-  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15145,7 +14871,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C17881-DAFD-4C84-A17F-55BBEAD03995}">
-  <sheetPr codeName="Sheet20"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -16128,7 +15853,6 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F709F27A-B438-425D-9CE5-4433D56D41EB}">
-  <sheetPr codeName="Sheet21"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -17157,7 +16881,6 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F8F46C-F54E-4291-B263-30F09581E207}">
-  <sheetPr codeName="Sheet22"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -18187,7 +17910,6 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678713E6-01EC-4AF8-B85B-EFBD12D6B70F}">
-  <sheetPr codeName="Sheet23"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -19144,7 +18866,6 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334ED2BD-C64B-41B3-9E46-E393C83DCE0D}">
-  <sheetPr codeName="Sheet24"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -20103,7 +19824,6 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0076AB3-51EE-48BC-AEC0-7BB9E3567B7B}">
-  <sheetPr codeName="Sheet25"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -21054,7 +20774,6 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B0924B-EDEF-4DF7-8455-9FD768646ACB}">
-  <sheetPr codeName="Sheet26"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -22022,7 +21741,6 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A3349F-C52E-4B58-A37E-71036D68DB5F}">
-  <sheetPr codeName="Sheet27"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -22978,7 +22696,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295EA6C7-41C0-4647-800C-73142E5C7312}">
-  <sheetPr codeName="Sheet28"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -23938,7 +23655,6 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDD0B73-E798-4DEF-9280-3A586EB1328D}">
-  <sheetPr codeName="Sheet29"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -24935,7 +24651,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7869E3E2-0C43-4B75-B037-88883C600F16}">
-  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -25902,7 +25617,6 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA70BF8E-E61E-4DD4-B092-05B5B84C146C}">
-  <sheetPr codeName="Sheet30"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -26854,7 +26568,6 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1512014-7E55-48A5-A156-301288989B5F}">
-  <sheetPr codeName="Sheet31"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27852,7 +27565,6 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0710C7B-494D-4CF5-BC4B-7BE46A9F7D6D}">
-  <sheetPr codeName="Sheet32"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -28809,7 +28521,6 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BCF6A8-6D74-4012-8D66-6C641AE2A83A}">
-  <sheetPr codeName="Sheet33"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -29763,7 +29474,6 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CDCF50-94E7-4073-8BC1-5C079BEFD9C1}">
-  <sheetPr codeName="Sheet34"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -30727,7 +30437,6 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6FF5E-0A25-4D27-9A2F-A750039A4021}">
-  <sheetPr codeName="Sheet35"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -31734,7 +31443,6 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0F0789-80DD-4D6D-BAEF-8354D45500C6}">
-  <sheetPr codeName="Sheet36"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -32708,7 +32416,6 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4377A38-767C-4E3A-9F5D-249D85B06EC0}">
-  <sheetPr codeName="Sheet37"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -33653,7 +33360,6 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFA1819-D690-482C-8C2A-B0A3D11E6489}">
-  <sheetPr codeName="Sheet38"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -34614,7 +34320,6 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE05AFB0-7C88-4CE5-8272-8F6FC78061E4}">
-  <sheetPr codeName="Sheet39"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -35594,7 +35299,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C30E9-5FB6-49A9-B6BD-FFF91FF66018}">
-  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -36556,7 +36260,6 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339F0ADB-EC8A-4414-B29C-BB02190C92C3}">
-  <sheetPr codeName="Sheet40"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37506,7 +37209,6 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C89191-B9A7-4B58-90DE-3BA1AC866D66}">
-  <sheetPr codeName="Sheet41"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -38456,7 +38158,6 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D961EB-8F82-44AB-8377-3106023C56AF}">
-  <sheetPr codeName="Sheet42"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -39442,7 +39143,6 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6768BE0-819D-489F-813B-79AE506BF05C}">
-  <sheetPr codeName="Sheet43"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -40416,7 +40116,6 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53562B77-777F-46DF-B9F6-984568C5E4CE}">
-  <sheetPr codeName="Sheet44"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -41423,3969 +41122,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AC2003-9C45-4AB3-BED1-87587F05F0E5}">
-  <sheetPr codeName="Sheet45"/>
-  <dimension ref="B2:N58"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="4.19921875" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D5" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D6" s="2">
-        <v>0.29166666666666702</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D7" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D8" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D9" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D10" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D11" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D12" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D13" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D14" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="9" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D15" s="2">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D16" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D17" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D18" s="2">
-        <v>0.54166666666666596</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D19" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.58333333333333404</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D20" s="2">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D21" s="2">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D22" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.64583333333333404</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D23" s="2">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D24" s="2">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D25" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.70833333333333404</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="9"/>
-    </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D26" s="2">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="9"/>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D27" s="2">
-        <v>0.72916666666666596</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.750000000000001</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D28" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.77083333333333404</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="9"/>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D29" s="2">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.79166666666666696</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="9"/>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D30" s="2">
-        <v>0.79166666666666596</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.812500000000001</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="9"/>
-    </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D31" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.83333333333333404</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D32" s="2">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D33" s="2">
-        <v>0.85416666666666596</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.875000000000001</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="9"/>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D34" s="2">
-        <v>0.874999999999999</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.89583333333333404</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="9"/>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D35" s="2">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.91666666666666696</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="9"/>
-    </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D36" s="2">
-        <v>0.91666666666666596</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.937500000000001</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D37" s="2">
-        <v>0.937499999999999</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.95833333333333404</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D38" s="2">
-        <v>0.95833333333333304</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.97916666666666796</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="L38" s="5"/>
-      <c r="M38" s="9"/>
-    </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D39" s="2">
-        <v>0.97916666666666596</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="9"/>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D40" s="2">
-        <v>0.999999999999999</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="9"/>
-    </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D41" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D42" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="9"/>
-    </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D43" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="9"/>
-    </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D44" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D45" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D46" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1.1458333333333399</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D47" s="2">
-        <v>1.1458333333333299</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D48" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D49" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>1.2083333333333399</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D50" s="2">
-        <v>1.2083333333333299</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1.2291666666666701</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="L58" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D54:J58"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M14" r:id="rId1" xr:uid="{874417D0-EA7B-4245-8500-C8B71E768239}"/>
-    <hyperlink ref="M16" r:id="rId2" xr:uid="{DA7B9483-2580-41F0-B6F5-194709095BE3}"/>
-    <hyperlink ref="M17" r:id="rId3" xr:uid="{E620ECFA-D74A-4CCF-B92D-9B83FCB4A309}"/>
-    <hyperlink ref="M18" r:id="rId4" xr:uid="{B2A94603-4625-4F0B-9D25-09B18A785B04}"/>
-    <hyperlink ref="M19" r:id="rId5" xr:uid="{7130C53A-83D8-436C-AB53-CB3FCF81D52E}"/>
-    <hyperlink ref="M15" r:id="rId6" xr:uid="{28E2A037-2E72-4270-9BB1-C103682AEC13}"/>
-    <hyperlink ref="K35" r:id="rId7" xr:uid="{3F29F36F-65AE-4EAB-B658-0E440B68158A}"/>
-    <hyperlink ref="K36" r:id="rId8" xr:uid="{7AC9A6B5-DA16-45C4-9539-386F5AAEA2CB}"/>
-    <hyperlink ref="K37" r:id="rId9" xr:uid="{3029B4C6-1641-4FB5-AB9F-8F30CAB4155C}"/>
-    <hyperlink ref="K38" r:id="rId10" xr:uid="{2C09844C-0624-4201-95F4-63DA773F2C10}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBDB166-6101-47CA-80A3-5991486736B1}">
-  <dimension ref="B2:N58"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="4.19921875" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D5" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D6" s="2">
-        <v>0.29166666666666702</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D7" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D8" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D9" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D10" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D11" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D12" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D13" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D14" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="9" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D15" s="2">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D16" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D17" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D18" s="2">
-        <v>0.54166666666666596</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D19" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.58333333333333404</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D20" s="2">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D21" s="2">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D22" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.64583333333333404</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D23" s="2">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D24" s="2">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D25" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.70833333333333404</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="9"/>
-    </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D26" s="2">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="9"/>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D27" s="2">
-        <v>0.72916666666666596</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.750000000000001</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D28" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.77083333333333404</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="9"/>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D29" s="2">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.79166666666666696</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="9"/>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D30" s="2">
-        <v>0.79166666666666596</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.812500000000001</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="9"/>
-    </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D31" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.83333333333333404</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D32" s="2">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D33" s="2">
-        <v>0.85416666666666596</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.875000000000001</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="9"/>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D34" s="2">
-        <v>0.874999999999999</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.89583333333333404</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="9"/>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D35" s="2">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.91666666666666696</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="9"/>
-    </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D36" s="2">
-        <v>0.91666666666666596</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.937500000000001</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D37" s="2">
-        <v>0.937499999999999</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.95833333333333404</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D38" s="2">
-        <v>0.95833333333333304</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.97916666666666796</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="L38" s="5"/>
-      <c r="M38" s="9"/>
-    </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D39" s="2">
-        <v>0.97916666666666596</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="9"/>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D40" s="2">
-        <v>0.999999999999999</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="L40" s="5"/>
-      <c r="M40" s="9"/>
-    </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D41" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D42" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="9"/>
-    </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D43" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="9"/>
-    </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D44" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D45" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D46" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1.1458333333333399</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D47" s="2">
-        <v>1.1458333333333299</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D48" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D49" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>1.2083333333333399</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D50" s="2">
-        <v>1.2083333333333299</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1.2291666666666701</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="L58" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D54:J58"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M14" r:id="rId1" xr:uid="{127C52AB-8F54-4CB4-930F-537CB5B24888}"/>
-    <hyperlink ref="M16" r:id="rId2" xr:uid="{90D152F9-C630-4A3A-85C3-BC413E33EDF4}"/>
-    <hyperlink ref="M17" r:id="rId3" xr:uid="{071F3FF9-0AD9-4BFE-817A-EE01411AF02A}"/>
-    <hyperlink ref="M18" r:id="rId4" xr:uid="{20847A6C-99F3-4760-9C93-8876CC2F2B0F}"/>
-    <hyperlink ref="M19" r:id="rId5" xr:uid="{9FBBD212-1082-4928-A229-0BF9A7EDDC25}"/>
-    <hyperlink ref="M15" r:id="rId6" xr:uid="{2ECB9528-2279-476B-826C-52D747B85E6F}"/>
-    <hyperlink ref="K34" r:id="rId7" xr:uid="{48EA548D-86DE-473F-A73C-3853E5738800}"/>
-    <hyperlink ref="K35" r:id="rId8" xr:uid="{F24B6437-1E3D-4746-96E3-49A44790DAC5}"/>
-    <hyperlink ref="K36" r:id="rId9" xr:uid="{91619E24-965D-478B-9168-A68665DF7AB5}"/>
-    <hyperlink ref="K37" r:id="rId10" xr:uid="{DE5C55A2-66A6-4C47-A28F-B096781FC84B}"/>
-    <hyperlink ref="K38" r:id="rId11" xr:uid="{D5CFD281-0C2B-44DF-B013-CDE6E8DC6DF1}"/>
-    <hyperlink ref="K39" r:id="rId12" xr:uid="{D86246C5-29CE-4F90-9E07-D5686C7B1C73}"/>
-    <hyperlink ref="K40" r:id="rId13" xr:uid="{73BDF172-03B6-4519-B1F6-03AA13A6336E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715C72A0-4896-4247-B188-D05AD34E38C3}">
-  <dimension ref="B2:N58"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="4.19921875" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46261</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D5" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D6" s="2">
-        <v>0.29166666666666702</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D7" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D8" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D9" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D10" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D11" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D12" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D13" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D14" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="9" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D15" s="2">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D16" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D17" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D18" s="2">
-        <v>0.54166666666666596</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D19" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.58333333333333404</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D20" s="2">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D21" s="2">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D22" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.64583333333333404</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D23" s="2">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D24" s="2">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D25" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.70833333333333404</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="9"/>
-    </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D26" s="2">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="9"/>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D27" s="2">
-        <v>0.72916666666666596</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.750000000000001</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D28" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.77083333333333404</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="9"/>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D29" s="2">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.79166666666666696</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="9"/>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D30" s="2">
-        <v>0.79166666666666596</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.812500000000001</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="9"/>
-    </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D31" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.83333333333333404</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D32" s="2">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D33" s="2">
-        <v>0.85416666666666596</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.875000000000001</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="9"/>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D34" s="2">
-        <v>0.874999999999999</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.89583333333333404</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="9"/>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D35" s="2">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.91666666666666696</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="9"/>
-    </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D36" s="2">
-        <v>0.91666666666666596</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.937500000000001</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D37" s="2">
-        <v>0.937499999999999</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.95833333333333404</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D38" s="2">
-        <v>0.95833333333333304</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.97916666666666796</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="L38" s="5"/>
-      <c r="M38" s="9"/>
-    </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D39" s="2">
-        <v>0.97916666666666596</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="9"/>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D40" s="2">
-        <v>0.999999999999999</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="L40" s="5"/>
-      <c r="M40" s="9"/>
-    </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D41" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D42" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="9"/>
-    </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D43" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="9"/>
-    </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D44" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D45" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D46" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1.1458333333333399</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D47" s="2">
-        <v>1.1458333333333299</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D48" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D49" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>1.2083333333333399</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D50" s="2">
-        <v>1.2083333333333299</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1.2291666666666701</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="L58" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D54:J58"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M14" r:id="rId1" xr:uid="{58B43F36-B281-4BEC-BF53-A2A57A48F50A}"/>
-    <hyperlink ref="M16" r:id="rId2" xr:uid="{EBDE1810-5F40-45CA-8F8D-16D979340D89}"/>
-    <hyperlink ref="M17" r:id="rId3" xr:uid="{DB07D43B-BA2F-4B03-9A82-2A6C65B2EF2D}"/>
-    <hyperlink ref="M18" r:id="rId4" xr:uid="{314BDC1B-885D-4EF2-90B4-3E6DBD7187C6}"/>
-    <hyperlink ref="M19" r:id="rId5" xr:uid="{454208C9-DBEB-427D-815F-C2A2533A322E}"/>
-    <hyperlink ref="M15" r:id="rId6" xr:uid="{64FA2FC7-7A61-4C06-8C5D-E38209D17D33}"/>
-    <hyperlink ref="K33" r:id="rId7" display="https://skillhub.jp/courses/581/lessons/4549" xr:uid="{BF67BB14-C2EF-4364-84E4-A5DD1698391D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AB0654-9A1F-4AF2-9885-EFB59B706C01}">
-  <dimension ref="B2:N58"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="4.19921875" customWidth="1"/>
-    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.19921875" customWidth="1"/>
-    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D5" s="2">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D6" s="2">
-        <v>0.29166666666666702</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D7" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D8" s="2">
-        <v>0.33333333333333298</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D9" s="2">
-        <v>0.35416666666666702</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D10" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D11" s="2">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D12" s="2">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D13" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="9"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D14" s="2">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="9"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D15" s="2">
-        <v>0.47916666666666602</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D16" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="9"/>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D17" s="2">
-        <v>0.52083333333333304</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="9"/>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D18" s="2">
-        <v>0.54166666666666596</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="9"/>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D19" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.58333333333333404</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="9"/>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D20" s="2">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D21" s="2">
-        <v>0.60416666666666596</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D22" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.64583333333333404</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D23" s="2">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D24" s="2">
-        <v>0.66666666666666596</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D25" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.70833333333333404</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="9"/>
-    </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D26" s="2">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="9"/>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D27" s="2">
-        <v>0.72916666666666596</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.750000000000001</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D28" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.77083333333333404</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="9"/>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D29" s="2">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.79166666666666696</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="9"/>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D30" s="2">
-        <v>0.79166666666666596</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.812500000000001</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="9"/>
-    </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D31" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.83333333333333404</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D32" s="2">
-        <v>0.83333333333333304</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D33" s="2">
-        <v>0.85416666666666596</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.875000000000001</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="9"/>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D34" s="2">
-        <v>0.874999999999999</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.89583333333333404</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="9"/>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D35" s="2">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.91666666666666696</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D36" s="2">
-        <v>0.91666666666666596</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.937500000000001</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="8"/>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D37" s="2">
-        <v>0.937499999999999</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.95833333333333404</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="8"/>
-    </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D38" s="2">
-        <v>0.95833333333333304</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.97916666666666796</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="9"/>
-    </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D39" s="2">
-        <v>0.97916666666666596</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="9"/>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D40" s="2">
-        <v>0.999999999999999</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="9"/>
-    </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D41" s="2">
-        <v>1.0208333333333299</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D42" s="2">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="9"/>
-    </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D43" s="2">
-        <v>1.0625</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="9"/>
-    </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D44" s="2">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D45" s="2">
-        <v>1.1041666666666701</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D46" s="2">
-        <v>1.125</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1.1458333333333399</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D47" s="2">
-        <v>1.1458333333333299</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
-      <c r="D48" s="2">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D49" s="2">
-        <v>1.1875</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <v>1.2083333333333399</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D50" s="2">
-        <v>1.2083333333333299</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1.2291666666666701</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D54" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="L58" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D54:J58"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="M35" r:id="rId1" xr:uid="{A47DB830-8494-4BFD-B22D-3774735AE73D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
-  <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -46360,7 +42098,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56A0045-9D53-4CC6-A5D6-D0144024C4B8}">
-  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -47331,7 +43068,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D6DC6F-267C-4F17-A216-7F3B96758D43}">
-  <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -48311,7 +44047,6 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5E7C19-79D0-44D8-B74F-21C9B37B6919}">
-  <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -49310,7 +45045,6 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A6C636-4572-4F93-A5EA-E88774DAB386}">
-  <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:N58"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>

--- a/document/日報.xlsx
+++ b/document/日報.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taket\docker-env\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645E2A2F-DD1C-4E00-A2FD-4AE54C48C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9F6611-FE1A-43A4-9197-FC9FDE44EF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="36" activeTab="46" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="38" activeTab="48" xr2:uid="{265D0D78-B26C-4260-A406-CF98F0C11782}"/>
   </bookViews>
   <sheets>
     <sheet name="8-1 (3)" sheetId="23" r:id="rId1"/>
@@ -60,6 +60,8 @@
     <sheet name="8-25" sheetId="46" r:id="rId45"/>
     <sheet name="8-26" sheetId="47" r:id="rId46"/>
     <sheet name="8-27" sheetId="48" r:id="rId47"/>
+    <sheet name="8-28" sheetId="49" r:id="rId48"/>
+    <sheet name="8-29" sheetId="50" r:id="rId49"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'8-2'!$H$31:$J$32</definedName>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="286">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -2714,6 +2716,64 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>htmlテーブル用に作成した機能と同様の機能を他テーブルにも実装</t>
+    <rPh sb="8" eb="9">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これまでhtml用に実装した機能を他テーブルにも実装。
+一通りの機能は作成完了した。
+(apiは未済)</t>
+    <rPh sb="8" eb="9">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒトトオ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="35" eb="39">
+      <t>サクセイカンリョウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ミサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -2821,7 +2881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2861,6 +2921,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -44373,6 +44436,2042 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4D082E-0353-4F49-B382-BC54813288F8}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="M14" r:id="rId1" xr:uid="{2124B170-31E1-49DD-B40E-C9896FAB30EE}"/>
+    <hyperlink ref="M16" r:id="rId2" xr:uid="{CC7DFF4C-99E8-45F5-89CA-359E6613DE08}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{08E4D86F-181E-4026-81D9-E6AD6C8E840A}"/>
+    <hyperlink ref="M18" r:id="rId4" xr:uid="{DE5251EB-DBC5-495D-ADCF-D72BEC323077}"/>
+    <hyperlink ref="M19" r:id="rId5" xr:uid="{6931BC5B-D6D4-49B8-8C94-C10B32686D2E}"/>
+    <hyperlink ref="M15" r:id="rId6" xr:uid="{5C7607E5-0BB0-43D5-80DA-B051E56E0FCF}"/>
+    <hyperlink ref="K33" r:id="rId7" display="https://skillhub.jp/courses/581/lessons/4549" xr:uid="{6C423FB8-2ECA-41E3-B582-E77D85F9955E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0944AD47-9B57-45E0-8315-51CA4E7C6065}">
+  <dimension ref="B2:N58"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.19921875" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.19921875" customWidth="1"/>
+    <col min="8" max="8" width="83.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5" customWidth="1"/>
+    <col min="13" max="13" width="3.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D5" s="2">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D6" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D7" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D8" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D9" s="2">
+        <v>0.35416666666666702</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D10" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D11" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D12" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D13" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D14" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D15" s="2">
+        <v>0.47916666666666602</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D17" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D18" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D19" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.58333333333333404</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D20" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D21" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D22" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D23" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D24" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D25" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70833333333333404</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D26" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="9"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D27" s="2">
+        <v>0.72916666666666596</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.750000000000001</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D28" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.77083333333333404</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D29" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D30" s="2">
+        <v>0.79166666666666596</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.812500000000001</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D33" s="2">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D34" s="2">
+        <v>0.874999999999999</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D35" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D36" s="2">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D37" s="2">
+        <v>0.937499999999999</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="9"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D38" s="2">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.97916666666666796</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="9"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D39" s="2">
+        <v>0.97916666666666596</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="9"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D40" s="2">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D41" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D42" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D43" s="2">
+        <v>1.0625</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D44" s="2">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D45" s="2">
+        <v>1.1041666666666701</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D46" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1458333333333399</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D47" s="2">
+        <v>1.1458333333333299</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D48" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D49" s="2">
+        <v>1.1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1.2083333333333399</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D50" s="2">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1.2291666666666701</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D54" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="L58" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D54:J58"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F16049-F3BA-43E6-ABE7-97E21F4E14BD}">
   <sheetPr codeName="Sheet5"/>
